--- a/docs/xlsx/jobs-2026-08-13.xlsx
+++ b/docs/xlsx/jobs-2026-08-13.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="824">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="872">
   <si>
     <t>Title</t>
   </si>
@@ -691,6 +691,27 @@
     <t>https://www.idealist.org/en/consultant-job/0e09b01938454769a8597a7cf3482131-accountant-part-time-as-needed-fohrman-fohrman-inc-dana-point</t>
   </si>
   <si>
+    <t>Accounting Manager</t>
+  </si>
+  <si>
+    <t>PRO Youth &amp; Families</t>
+  </si>
+  <si>
+    <t>Sacramento, California</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 33.00 - 40.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dc9473490f0c41e693138fd69f90b8f2-accounting-manager-pro-youth-families-sacramento</t>
+  </si>
+  <si>
     <t>Accounts Payable Coordinator</t>
   </si>
   <si>
@@ -700,9 +721,6 @@
     <t>Washington, District of Columbia</t>
   </si>
   <si>
-    <t>Full Time</t>
-  </si>
-  <si>
     <t>USD 50000.00 - 55000.00/year</t>
   </si>
   <si>
@@ -715,9 +733,6 @@
     <t>Mercy Housing California</t>
   </si>
   <si>
-    <t>Sacramento, California</t>
-  </si>
-  <si>
     <t>USD 80000.00 - 90000.00/year</t>
   </si>
   <si>
@@ -1321,6 +1336,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/5298357f00c24311920a3be2081fbcac-director-individual-giving-spoonfuls-newton</t>
   </si>
   <si>
+    <t>Early College Awareness College Access Program Specialist</t>
+  </si>
+  <si>
+    <t>CollegeBound Foundation</t>
+  </si>
+  <si>
+    <t>Baltimore, Maryland</t>
+  </si>
+  <si>
+    <t>USD 56000.00 - 61000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f87c5043f2424338aaee35fea9bd8f2d-early-college-awareness-college-access-program-specialist-collegebound-foundation-baltimore</t>
+  </si>
+  <si>
     <t>Executive Director</t>
   </si>
   <si>
@@ -1669,6 +1702,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/c78bf4c9d64742fea0303e735480d94b-intake-specialist-bilingual-mental-health-advocacy-services-inc-glendale</t>
   </si>
   <si>
+    <t>IPF Atid Program Coordinator - Washington, D.C.</t>
+  </si>
+  <si>
+    <t>USD 62500.00 - 72500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/43e540c576854f2dbda75a86b11ba9a8-ipf-atid-program-coordinator-washington-dc-israel-policy-forum-washington</t>
+  </si>
+  <si>
     <t>Lead Organizer</t>
   </si>
   <si>
@@ -1780,6 +1822,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/43a1c24002c640ca976458d2978d8f86-manager-strategic-alliances-new-business-first-book-washington</t>
   </si>
   <si>
+    <t>Managing Attorney (Hillsboro Regional Office)</t>
+  </si>
+  <si>
+    <t>Oregon Law Center</t>
+  </si>
+  <si>
+    <t>Hillsboro, Oregon</t>
+  </si>
+  <si>
+    <t>USD 84000.00 - 127000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d86f653b3c1f44f18b4d3a9323e9d503-managing-attorney-hillsboro-regional-office-oregon-law-center-hillsboro</t>
+  </si>
+  <si>
     <t>Managing Director, School Strategy and Investments</t>
   </si>
   <si>
@@ -1792,6 +1852,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/2f7c312c28f4452a9c08bd19bbcf0194-managing-director-school-strategy-and-investments-rochester-education-and-development-for-youth-ready-rochester</t>
   </si>
   <si>
+    <t>Marketing and Events Manager</t>
+  </si>
+  <si>
+    <t>Friends &amp; Foundation of the Rochester Public Library</t>
+  </si>
+  <si>
+    <t>Rochester, New York</t>
+  </si>
+  <si>
+    <t>USD 58000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4ebfd01776574697b486642023895252-marketing-and-events-manager-friends-foundation-of-the-rochester-public-library-rochester</t>
+  </si>
+  <si>
     <t>Mobile Crisis Team Clinician Full-Time Positions Available in Queens &amp; Brooklyn</t>
   </si>
   <si>
@@ -1837,6 +1915,12 @@
     <t>https://www.idealist.org/en/nonprofit-job/3c4f8a43df5f4faeb2184236eb312f11-national-program-assistant-americorps-employment-navigators-one-world-link-atlanta</t>
   </si>
   <si>
+    <t>National Program Manager-AmeriCorps Employment Navigators</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3c4f8a43df5f4faeb2184236eb312f11-national-program-manager-americorps-employment-navigators-one-world-link-atlanta</t>
+  </si>
+  <si>
     <t>New York Organizer &amp; Campaigner</t>
   </si>
   <si>
@@ -1942,6 +2026,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/e807085dbd0e403ba7fb47fa3653244a-organizer-youth-represent-new-york</t>
   </si>
   <si>
+    <t>Organizing Director</t>
+  </si>
+  <si>
+    <t>Center for Workers' Rights</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace, Legal Assistance, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a46286a5c81d4eda83caf37fa39715f9-organizing-director-center-for-workers-rights-sacramento</t>
+  </si>
+  <si>
     <t>Part Time Accountant</t>
   </si>
   <si>
@@ -2239,6 +2338,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/f1d6a1ad46084f39abf8cf4640c28da2-service-enriched-housing-super-hero-community-housing-resource-partners-inc-arlington</t>
   </si>
   <si>
+    <t>Social Worker / Senior Social Worker</t>
+  </si>
+  <si>
+    <t>Legal Services for Children</t>
+  </si>
+  <si>
+    <t>USD 80474.00 - 108612.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6668bf82d1cb4d8ea96d7b096c42e642-social-worker-senior-social-worker-legal-services-for-children-san-francisco</t>
+  </si>
+  <si>
     <t>Social Worker Supervisor - Queens Older Adult Centers</t>
   </si>
   <si>
@@ -2278,9 +2392,6 @@
     <t>USD 70000.00 - 80000.00/year</t>
   </si>
   <si>
-    <t>Legal Assistance</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/279683cd68e941a894e517919d05aa12-staff-attorney-volunteer-lawyers-project-of-the-boston-bar-association-boston</t>
   </si>
   <si>
@@ -2356,6 +2467,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/9bb647da71614bc09bfb431e1be1accf-toddler-teacher-seola-gardens-neighborhood-house-seattle</t>
   </si>
   <si>
+    <t>Tutoring Program Coordinator(Prince George's County)</t>
+  </si>
+  <si>
+    <t>Community Services Foundation</t>
+  </si>
+  <si>
+    <t>SEAT PLEASANT, Maryland</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 22.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Financial Literacy Personal Finance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/71cc5a5d669f4e8ea5d78c9a3c80b6a7-tutoring-program-coordinatorprince-georges-county-community-services-foundation-seat-pleasant</t>
+  </si>
+  <si>
     <t>Vice President of Finance and Operations (candidates can be based anywhere in the US, preference for EST)</t>
   </si>
   <si>
@@ -2447,6 +2576,21 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/business-job/ee046e8af04d444c87a3e23cbb17a465-voter-outreach-team-lead-oakland-rising-action-center-for-empowered-politics-oakland</t>
+  </si>
+  <si>
+    <t>We are hiring Field Directors to manage our office in Springfield and Lee’s Summit, MO!</t>
+  </si>
+  <si>
+    <t>The Outreach Team</t>
+  </si>
+  <si>
+    <t>Springfield, Missouri</t>
+  </si>
+  <si>
+    <t>USD 1146.00 - 1500.00/week</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/e559013ffffe40a7a2d3596d40a1ec2c-we-are-hiring-field-directors-to-manage-our-office-in-springfield-and-lees-summit-mo-the-outreach-team-springfield</t>
   </si>
   <si>
     <t>West Coast Organizing Manager</t>
@@ -3958,7 +4102,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H132"/>
+  <dimension ref="A1:H142"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -4037,44 +4181,44 @@
         <v>229</v>
       </c>
       <c r="F3" t="s">
-        <v>101</v>
+        <v>230</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D4" t="s">
         <v>228</v>
       </c>
       <c r="E4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F4" t="s">
         <v>101</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C5" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="D5" t="s">
         <v>228</v>
@@ -4083,110 +4227,110 @@
         <v>239</v>
       </c>
       <c r="F5" t="s">
+        <v>101</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>240</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>241</v>
+      </c>
+      <c r="B6" t="s">
         <v>242</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>243</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
+        <v>228</v>
+      </c>
+      <c r="E6" t="s">
         <v>244</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
         <v>245</v>
       </c>
-      <c r="E6" t="s">
+      <c r="H6" s="2" t="s">
         <v>246</v>
-      </c>
-      <c r="F6" t="s">
-        <v>247</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>247</v>
+      </c>
+      <c r="B7" t="s">
+        <v>248</v>
+      </c>
+      <c r="C7" t="s">
         <v>249</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" t="s">
         <v>250</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
         <v>251</v>
       </c>
-      <c r="D7" t="s">
-        <v>245</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>252</v>
       </c>
-      <c r="F7" t="s">
+      <c r="H7" s="2" t="s">
         <v>253</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>254</v>
+      </c>
+      <c r="B8" t="s">
         <v>255</v>
-      </c>
-      <c r="B8" t="s">
-        <v>250</v>
       </c>
       <c r="C8" t="s">
         <v>256</v>
       </c>
       <c r="D8" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E8" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F8" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>260</v>
+      </c>
+      <c r="B9" t="s">
+        <v>255</v>
+      </c>
+      <c r="C9" t="s">
+        <v>261</v>
+      </c>
+      <c r="D9" t="s">
+        <v>250</v>
+      </c>
+      <c r="E9" t="s">
+        <v>257</v>
+      </c>
+      <c r="F9" t="s">
         <v>258</v>
       </c>
-      <c r="B9" t="s">
-        <v>259</v>
-      </c>
-      <c r="C9" t="s">
-        <v>260</v>
-      </c>
-      <c r="D9" t="s">
-        <v>228</v>
-      </c>
-      <c r="E9" t="s">
-        <v>261</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="H9" s="2" t="s">
         <v>262</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>263</v>
+      </c>
+      <c r="B10" t="s">
         <v>264</v>
-      </c>
-      <c r="B10" t="s">
-        <v>259</v>
       </c>
       <c r="C10" t="s">
         <v>265</v>
@@ -4198,53 +4342,53 @@
         <v>266</v>
       </c>
       <c r="F10" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B11" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="C11" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="D11" t="s">
         <v>228</v>
       </c>
       <c r="E11" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="F11" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B12" t="s">
+        <v>264</v>
+      </c>
+      <c r="C12" t="s">
+        <v>265</v>
+      </c>
+      <c r="D12" t="s">
+        <v>228</v>
+      </c>
+      <c r="E12" t="s">
         <v>271</v>
       </c>
-      <c r="C12" t="s">
-        <v>227</v>
-      </c>
-      <c r="D12" t="s">
-        <v>228</v>
-      </c>
-      <c r="E12" t="s">
-        <v>272</v>
-      </c>
       <c r="F12" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>274</v>
@@ -4258,13 +4402,13 @@
         <v>276</v>
       </c>
       <c r="C13" t="s">
+        <v>234</v>
+      </c>
+      <c r="D13" t="s">
+        <v>228</v>
+      </c>
+      <c r="E13" t="s">
         <v>277</v>
-      </c>
-      <c r="D13" t="s">
-        <v>228</v>
-      </c>
-      <c r="E13" t="s">
-        <v>101</v>
       </c>
       <c r="F13" t="s">
         <v>278</v>
@@ -4284,50 +4428,50 @@
         <v>282</v>
       </c>
       <c r="D14" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="E14" t="s">
+        <v>101</v>
+      </c>
+      <c r="F14" t="s">
         <v>283</v>
       </c>
-      <c r="F14" t="s">
+      <c r="H14" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>285</v>
+      </c>
+      <c r="B15" t="s">
         <v>286</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>287</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
+        <v>250</v>
+      </c>
+      <c r="E15" t="s">
         <v>288</v>
       </c>
-      <c r="D15" t="s">
-        <v>228</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>289</v>
       </c>
-      <c r="F15" t="s">
+      <c r="H15" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>291</v>
+      </c>
+      <c r="B16" t="s">
         <v>292</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>293</v>
-      </c>
-      <c r="C16" t="s">
-        <v>215</v>
       </c>
       <c r="D16" t="s">
         <v>228</v>
@@ -4350,56 +4494,56 @@
         <v>298</v>
       </c>
       <c r="C17" t="s">
+        <v>215</v>
+      </c>
+      <c r="D17" t="s">
+        <v>228</v>
+      </c>
+      <c r="E17" t="s">
         <v>299</v>
       </c>
-      <c r="D17" t="s">
-        <v>228</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>300</v>
       </c>
-      <c r="F17" t="s">
+      <c r="H17" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>302</v>
+      </c>
+      <c r="B18" t="s">
         <v>303</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>304</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
+        <v>228</v>
+      </c>
+      <c r="E18" t="s">
         <v>305</v>
       </c>
-      <c r="D18" t="s">
-        <v>222</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>306</v>
       </c>
-      <c r="F18" t="s">
+      <c r="H18" s="2" t="s">
         <v>307</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>308</v>
+      </c>
+      <c r="B19" t="s">
         <v>309</v>
-      </c>
-      <c r="B19" t="s">
-        <v>250</v>
       </c>
       <c r="C19" t="s">
         <v>310</v>
       </c>
       <c r="D19" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="E19" t="s">
         <v>311</v>
@@ -4416,13 +4560,13 @@
         <v>314</v>
       </c>
       <c r="B20" t="s">
+        <v>255</v>
+      </c>
+      <c r="C20" t="s">
         <v>315</v>
       </c>
-      <c r="C20" t="s">
-        <v>227</v>
-      </c>
       <c r="D20" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="E20" t="s">
         <v>316</v>
@@ -4442,30 +4586,30 @@
         <v>320</v>
       </c>
       <c r="C21" t="s">
+        <v>234</v>
+      </c>
+      <c r="D21" t="s">
+        <v>228</v>
+      </c>
+      <c r="E21" t="s">
         <v>321</v>
       </c>
-      <c r="D21" t="s">
-        <v>228</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>322</v>
       </c>
-      <c r="F21" t="s">
+      <c r="H21" s="2" t="s">
         <v>323</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>324</v>
+      </c>
+      <c r="B22" t="s">
         <v>325</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>326</v>
-      </c>
-      <c r="C22" t="s">
-        <v>215</v>
       </c>
       <c r="D22" t="s">
         <v>228</v>
@@ -4474,21 +4618,21 @@
         <v>327</v>
       </c>
       <c r="F22" t="s">
-        <v>101</v>
+        <v>328</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B23" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C23" t="s">
-        <v>331</v>
+        <v>215</v>
       </c>
       <c r="D23" t="s">
         <v>228</v>
@@ -4497,21 +4641,21 @@
         <v>332</v>
       </c>
       <c r="F23" t="s">
+        <v>101</v>
+      </c>
+      <c r="H23" s="2" t="s">
         <v>333</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>334</v>
+      </c>
+      <c r="B24" t="s">
         <v>335</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>336</v>
-      </c>
-      <c r="C24" t="s">
-        <v>215</v>
       </c>
       <c r="D24" t="s">
         <v>228</v>
@@ -4534,13 +4678,13 @@
         <v>341</v>
       </c>
       <c r="C25" t="s">
+        <v>215</v>
+      </c>
+      <c r="D25" t="s">
+        <v>228</v>
+      </c>
+      <c r="E25" t="s">
         <v>342</v>
-      </c>
-      <c r="D25" t="s">
-        <v>228</v>
-      </c>
-      <c r="E25" t="s">
-        <v>101</v>
       </c>
       <c r="F25" t="s">
         <v>343</v>
@@ -4560,30 +4704,30 @@
         <v>347</v>
       </c>
       <c r="D26" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="E26" t="s">
+        <v>101</v>
+      </c>
+      <c r="F26" t="s">
         <v>348</v>
       </c>
-      <c r="F26" t="s">
+      <c r="H26" s="2" t="s">
         <v>349</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>350</v>
+      </c>
+      <c r="B27" t="s">
         <v>351</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>352</v>
       </c>
-      <c r="C27" t="s">
-        <v>233</v>
-      </c>
       <c r="D27" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="E27" t="s">
         <v>353</v>
@@ -4603,105 +4747,105 @@
         <v>357</v>
       </c>
       <c r="C28" t="s">
+        <v>227</v>
+      </c>
+      <c r="D28" t="s">
+        <v>228</v>
+      </c>
+      <c r="E28" t="s">
         <v>358</v>
       </c>
-      <c r="D28" t="s">
-        <v>228</v>
-      </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>359</v>
       </c>
-      <c r="F28" t="s">
+      <c r="H28" s="2" t="s">
         <v>360</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>361</v>
+      </c>
+      <c r="B29" t="s">
         <v>362</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>363</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
+        <v>228</v>
+      </c>
+      <c r="E29" t="s">
         <v>364</v>
       </c>
-      <c r="D29" t="s">
-        <v>228</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>365</v>
       </c>
-      <c r="F29" t="s">
+      <c r="H29" s="2" t="s">
         <v>366</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>367</v>
+      </c>
+      <c r="B30" t="s">
         <v>368</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>369</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
+        <v>228</v>
+      </c>
+      <c r="E30" t="s">
         <v>370</v>
       </c>
-      <c r="D30" t="s">
-        <v>228</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>371</v>
       </c>
-      <c r="F30" t="s">
+      <c r="H30" s="2" t="s">
         <v>372</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>373</v>
+      </c>
+      <c r="B31" t="s">
         <v>374</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>375</v>
       </c>
-      <c r="C31" t="s">
-        <v>227</v>
-      </c>
       <c r="D31" t="s">
         <v>228</v>
       </c>
       <c r="E31" t="s">
-        <v>322</v>
+        <v>376</v>
       </c>
       <c r="F31" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B32" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C32" t="s">
-        <v>379</v>
+        <v>234</v>
       </c>
       <c r="D32" t="s">
         <v>228</v>
       </c>
       <c r="E32" t="s">
-        <v>380</v>
+        <v>327</v>
       </c>
       <c r="F32" t="s">
         <v>381</v>
@@ -4712,91 +4856,91 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>379</v>
+      </c>
+      <c r="B33" t="s">
         <v>383</v>
       </c>
-      <c r="B33" t="s">
-        <v>298</v>
-      </c>
       <c r="C33" t="s">
-        <v>299</v>
+        <v>384</v>
       </c>
       <c r="D33" t="s">
         <v>228</v>
       </c>
       <c r="E33" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F33" t="s">
-        <v>301</v>
+        <v>386</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="B34" t="s">
-        <v>386</v>
+        <v>303</v>
       </c>
       <c r="C34" t="s">
-        <v>370</v>
+        <v>304</v>
       </c>
       <c r="D34" t="s">
         <v>228</v>
       </c>
       <c r="E34" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F34" t="s">
-        <v>388</v>
+        <v>306</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B35" t="s">
         <v>391</v>
       </c>
       <c r="C35" t="s">
+        <v>375</v>
+      </c>
+      <c r="D35" t="s">
+        <v>228</v>
+      </c>
+      <c r="E35" t="s">
         <v>392</v>
       </c>
-      <c r="D35" t="s">
-        <v>228</v>
-      </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>393</v>
       </c>
-      <c r="F35" t="s">
+      <c r="H35" s="2" t="s">
         <v>394</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>395</v>
+      </c>
+      <c r="B36" t="s">
         <v>396</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>397</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
+        <v>228</v>
+      </c>
+      <c r="E36" t="s">
         <v>398</v>
       </c>
-      <c r="D36" t="s">
-        <v>228</v>
-      </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>399</v>
-      </c>
-      <c r="F36" t="s">
-        <v>101</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>400</v>
@@ -4810,16 +4954,16 @@
         <v>402</v>
       </c>
       <c r="C37" t="s">
-        <v>215</v>
+        <v>403</v>
       </c>
       <c r="D37" t="s">
         <v>228</v>
       </c>
       <c r="E37" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F37" t="s">
-        <v>404</v>
+        <v>101</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>405</v>
@@ -4842,18 +4986,18 @@
         <v>408</v>
       </c>
       <c r="F38" t="s">
-        <v>101</v>
+        <v>409</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B39" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C39" t="s">
         <v>215</v>
@@ -4862,10 +5006,10 @@
         <v>228</v>
       </c>
       <c r="E39" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F39" t="s">
-        <v>413</v>
+        <v>101</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>414</v>
@@ -4879,13 +5023,13 @@
         <v>416</v>
       </c>
       <c r="C40" t="s">
+        <v>215</v>
+      </c>
+      <c r="D40" t="s">
+        <v>228</v>
+      </c>
+      <c r="E40" t="s">
         <v>417</v>
-      </c>
-      <c r="D40" t="s">
-        <v>228</v>
-      </c>
-      <c r="E40" t="s">
-        <v>234</v>
       </c>
       <c r="F40" t="s">
         <v>418</v>
@@ -4902,13 +5046,13 @@
         <v>421</v>
       </c>
       <c r="C41" t="s">
-        <v>78</v>
+        <v>422</v>
       </c>
       <c r="D41" t="s">
         <v>228</v>
       </c>
       <c r="E41" t="s">
-        <v>422</v>
+        <v>239</v>
       </c>
       <c r="F41" t="s">
         <v>423</v>
@@ -4925,7 +5069,7 @@
         <v>426</v>
       </c>
       <c r="C42" t="s">
-        <v>370</v>
+        <v>78</v>
       </c>
       <c r="D42" t="s">
         <v>228</v>
@@ -4934,21 +5078,21 @@
         <v>427</v>
       </c>
       <c r="F42" t="s">
-        <v>101</v>
+        <v>428</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B43" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C43" t="s">
-        <v>431</v>
+        <v>375</v>
       </c>
       <c r="D43" t="s">
         <v>228</v>
@@ -4957,38 +5101,38 @@
         <v>432</v>
       </c>
       <c r="F43" t="s">
+        <v>101</v>
+      </c>
+      <c r="H43" s="2" t="s">
         <v>433</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>434</v>
+      </c>
+      <c r="B44" t="s">
         <v>435</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>436</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
+        <v>228</v>
+      </c>
+      <c r="E44" t="s">
         <v>437</v>
       </c>
-      <c r="D44" t="s">
-        <v>228</v>
-      </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>438</v>
       </c>
-      <c r="F44" t="s">
+      <c r="H44" s="2" t="s">
         <v>439</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="B45" t="s">
         <v>441</v>
@@ -5034,252 +5178,252 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>446</v>
+      </c>
+      <c r="B47" t="s">
         <v>452</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
         <v>453</v>
       </c>
-      <c r="C47" t="s">
-        <v>215</v>
-      </c>
       <c r="D47" t="s">
         <v>228</v>
       </c>
       <c r="E47" t="s">
-        <v>101</v>
+        <v>454</v>
       </c>
       <c r="F47" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B48" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C48" t="s">
-        <v>364</v>
+        <v>459</v>
       </c>
       <c r="D48" t="s">
         <v>228</v>
       </c>
       <c r="E48" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="F48" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B49" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C49" t="s">
-        <v>463</v>
+        <v>215</v>
       </c>
       <c r="D49" t="s">
-        <v>464</v>
+        <v>228</v>
       </c>
       <c r="E49" t="s">
+        <v>101</v>
+      </c>
+      <c r="F49" t="s">
         <v>465</v>
       </c>
-      <c r="F49" t="s">
+      <c r="H49" s="2" t="s">
         <v>466</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="B50" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="C50" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D50" t="s">
-        <v>464</v>
+        <v>228</v>
       </c>
       <c r="E50" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="F50" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B51" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C51" t="s">
-        <v>215</v>
+        <v>474</v>
       </c>
       <c r="D51" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="E51" t="s">
-        <v>246</v>
+        <v>476</v>
       </c>
       <c r="F51" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B52" t="s">
+        <v>473</v>
+      </c>
+      <c r="C52" t="s">
+        <v>375</v>
+      </c>
+      <c r="D52" t="s">
         <v>475</v>
       </c>
-      <c r="C52" t="s">
+      <c r="E52" t="s">
         <v>476</v>
       </c>
-      <c r="D52" t="s">
-        <v>228</v>
-      </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
         <v>477</v>
       </c>
-      <c r="F52" t="s">
-        <v>101</v>
-      </c>
       <c r="H52" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B53" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C53" t="s">
-        <v>310</v>
+        <v>215</v>
       </c>
       <c r="D53" t="s">
-        <v>228</v>
+        <v>482</v>
       </c>
       <c r="E53" t="s">
-        <v>481</v>
+        <v>251</v>
       </c>
       <c r="F53" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B54" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C54" t="s">
-        <v>215</v>
+        <v>487</v>
       </c>
       <c r="D54" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="E54" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="F54" t="s">
-        <v>253</v>
+        <v>101</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B55" t="s">
-        <v>259</v>
+        <v>491</v>
       </c>
       <c r="C55" t="s">
-        <v>489</v>
+        <v>315</v>
       </c>
       <c r="D55" t="s">
         <v>228</v>
       </c>
       <c r="E55" t="s">
-        <v>261</v>
+        <v>492</v>
       </c>
       <c r="F55" t="s">
-        <v>262</v>
+        <v>493</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B56" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="C56" t="s">
-        <v>370</v>
+        <v>215</v>
       </c>
       <c r="D56" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="E56" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="F56" t="s">
-        <v>494</v>
+        <v>258</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="B57" t="s">
-        <v>497</v>
+        <v>264</v>
       </c>
       <c r="C57" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="D57" t="s">
-        <v>471</v>
+        <v>228</v>
       </c>
       <c r="E57" t="s">
-        <v>499</v>
+        <v>266</v>
       </c>
       <c r="F57" t="s">
-        <v>500</v>
+        <v>267</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>501</v>
@@ -5293,33 +5437,33 @@
         <v>503</v>
       </c>
       <c r="C58" t="s">
+        <v>375</v>
+      </c>
+      <c r="D58" t="s">
+        <v>228</v>
+      </c>
+      <c r="E58" t="s">
         <v>504</v>
       </c>
-      <c r="D58" t="s">
-        <v>228</v>
-      </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
         <v>505</v>
       </c>
-      <c r="F58" t="s">
+      <c r="H58" s="2" t="s">
         <v>506</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>507</v>
+      </c>
+      <c r="B59" t="s">
         <v>508</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C59" t="s">
         <v>509</v>
       </c>
-      <c r="C59" t="s">
-        <v>370</v>
-      </c>
       <c r="D59" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="E59" t="s">
         <v>510</v>
@@ -5336,108 +5480,108 @@
         <v>513</v>
       </c>
       <c r="B60" t="s">
-        <v>492</v>
+        <v>514</v>
       </c>
       <c r="C60" t="s">
-        <v>370</v>
+        <v>515</v>
       </c>
       <c r="D60" t="s">
         <v>228</v>
       </c>
       <c r="E60" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="F60" t="s">
-        <v>494</v>
+        <v>517</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B61" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="C61" t="s">
-        <v>227</v>
+        <v>375</v>
       </c>
       <c r="D61" t="s">
-        <v>228</v>
+        <v>475</v>
       </c>
       <c r="E61" t="s">
-        <v>337</v>
+        <v>521</v>
       </c>
       <c r="F61" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B62" t="s">
-        <v>521</v>
+        <v>503</v>
       </c>
       <c r="C62" t="s">
-        <v>522</v>
+        <v>375</v>
       </c>
       <c r="D62" t="s">
         <v>228</v>
       </c>
       <c r="E62" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="F62" t="s">
-        <v>524</v>
+        <v>505</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B63" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C63" t="s">
-        <v>528</v>
+        <v>234</v>
       </c>
       <c r="D63" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="E63" t="s">
+        <v>342</v>
+      </c>
+      <c r="F63" t="s">
         <v>529</v>
       </c>
-      <c r="F63" t="s">
+      <c r="H63" s="2" t="s">
         <v>530</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>531</v>
+      </c>
+      <c r="B64" t="s">
         <v>532</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
         <v>533</v>
       </c>
-      <c r="C64" t="s">
+      <c r="D64" t="s">
+        <v>228</v>
+      </c>
+      <c r="E64" t="s">
         <v>534</v>
-      </c>
-      <c r="D64" t="s">
-        <v>228</v>
-      </c>
-      <c r="E64" t="s">
-        <v>101</v>
       </c>
       <c r="F64" t="s">
         <v>535</v>
@@ -5454,82 +5598,82 @@
         <v>538</v>
       </c>
       <c r="C65" t="s">
-        <v>370</v>
+        <v>539</v>
       </c>
       <c r="D65" t="s">
-        <v>222</v>
+        <v>250</v>
       </c>
       <c r="E65" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F65" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B66" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C66" t="s">
-        <v>370</v>
+        <v>545</v>
       </c>
       <c r="D66" t="s">
         <v>228</v>
       </c>
       <c r="E66" t="s">
-        <v>499</v>
+        <v>101</v>
       </c>
       <c r="F66" t="s">
-        <v>101</v>
+        <v>546</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="B67" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="C67" t="s">
-        <v>547</v>
+        <v>375</v>
       </c>
       <c r="D67" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="E67" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="F67" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B68" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C68" t="s">
-        <v>553</v>
+        <v>375</v>
       </c>
       <c r="D68" t="s">
         <v>228</v>
       </c>
       <c r="E68" t="s">
-        <v>554</v>
+        <v>510</v>
       </c>
       <c r="F68" t="s">
         <v>101</v>
@@ -5546,30 +5690,30 @@
         <v>557</v>
       </c>
       <c r="C69" t="s">
-        <v>442</v>
+        <v>558</v>
       </c>
       <c r="D69" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="E69" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="F69" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B70" t="s">
-        <v>562</v>
+        <v>503</v>
       </c>
       <c r="C70" t="s">
-        <v>370</v>
+        <v>234</v>
       </c>
       <c r="D70" t="s">
         <v>228</v>
@@ -5578,30 +5722,30 @@
         <v>563</v>
       </c>
       <c r="F70" t="s">
+        <v>505</v>
+      </c>
+      <c r="H70" s="2" t="s">
         <v>564</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>565</v>
+      </c>
+      <c r="B71" t="s">
         <v>566</v>
       </c>
-      <c r="B71" t="s">
-        <v>357</v>
-      </c>
       <c r="C71" t="s">
-        <v>358</v>
+        <v>567</v>
       </c>
       <c r="D71" t="s">
         <v>228</v>
       </c>
       <c r="E71" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F71" t="s">
-        <v>568</v>
+        <v>101</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>569</v>
@@ -5615,7 +5759,7 @@
         <v>571</v>
       </c>
       <c r="C72" t="s">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="D72" t="s">
         <v>228</v>
@@ -5638,10 +5782,10 @@
         <v>576</v>
       </c>
       <c r="C73" t="s">
-        <v>215</v>
+        <v>375</v>
       </c>
       <c r="D73" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="E73" t="s">
         <v>577</v>
@@ -5658,33 +5802,33 @@
         <v>580</v>
       </c>
       <c r="B74" t="s">
+        <v>362</v>
+      </c>
+      <c r="C74" t="s">
+        <v>363</v>
+      </c>
+      <c r="D74" t="s">
+        <v>228</v>
+      </c>
+      <c r="E74" t="s">
         <v>581</v>
       </c>
-      <c r="C74" t="s">
-        <v>370</v>
-      </c>
-      <c r="D74" t="s">
-        <v>228</v>
-      </c>
-      <c r="E74" t="s">
+      <c r="F74" t="s">
         <v>582</v>
       </c>
-      <c r="F74" t="s">
+      <c r="H74" s="2" t="s">
         <v>583</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>584</v>
+      </c>
+      <c r="B75" t="s">
         <v>585</v>
       </c>
-      <c r="B75" t="s">
-        <v>421</v>
-      </c>
       <c r="C75" t="s">
-        <v>78</v>
+        <v>453</v>
       </c>
       <c r="D75" t="s">
         <v>228</v>
@@ -5693,122 +5837,122 @@
         <v>586</v>
       </c>
       <c r="F75" t="s">
-        <v>423</v>
+        <v>587</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B76" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C76" t="s">
         <v>215</v>
       </c>
       <c r="D76" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="E76" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="F76" t="s">
-        <v>253</v>
+        <v>592</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B77" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C77" t="s">
-        <v>528</v>
+        <v>375</v>
       </c>
       <c r="D77" t="s">
         <v>228</v>
       </c>
       <c r="E77" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="F77" t="s">
-        <v>101</v>
+        <v>597</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="B78" t="s">
-        <v>597</v>
+        <v>426</v>
       </c>
       <c r="C78" t="s">
-        <v>215</v>
+        <v>78</v>
       </c>
       <c r="D78" t="s">
         <v>228</v>
       </c>
       <c r="E78" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="F78" t="s">
-        <v>599</v>
+        <v>428</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B79" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C79" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D79" t="s">
         <v>228</v>
       </c>
       <c r="E79" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="F79" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B80" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C80" t="s">
-        <v>370</v>
+        <v>215</v>
       </c>
       <c r="D80" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="E80" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="F80" t="s">
-        <v>610</v>
+        <v>258</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>611</v>
@@ -5819,56 +5963,56 @@
         <v>612</v>
       </c>
       <c r="B81" t="s">
-        <v>101</v>
+        <v>613</v>
       </c>
       <c r="C81" t="s">
-        <v>215</v>
+        <v>614</v>
       </c>
       <c r="D81" t="s">
         <v>228</v>
       </c>
       <c r="E81" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="F81" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B82" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C82" t="s">
-        <v>215</v>
+        <v>539</v>
       </c>
       <c r="D82" t="s">
         <v>228</v>
       </c>
       <c r="E82" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="F82" t="s">
-        <v>619</v>
+        <v>101</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B83" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C83" t="s">
-        <v>623</v>
+        <v>215</v>
       </c>
       <c r="D83" t="s">
         <v>228</v>
@@ -5891,177 +6035,177 @@
         <v>628</v>
       </c>
       <c r="C84" t="s">
-        <v>310</v>
+        <v>629</v>
       </c>
       <c r="D84" t="s">
         <v>228</v>
       </c>
       <c r="E84" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="F84" t="s">
-        <v>459</v>
+        <v>631</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>633</v>
+      </c>
+      <c r="B85" t="s">
+        <v>628</v>
+      </c>
+      <c r="C85" t="s">
+        <v>629</v>
+      </c>
+      <c r="D85" t="s">
+        <v>228</v>
+      </c>
+      <c r="E85" t="s">
+        <v>630</v>
+      </c>
+      <c r="F85" t="s">
         <v>631</v>
       </c>
-      <c r="B85" t="s">
-        <v>632</v>
-      </c>
-      <c r="C85" t="s">
-        <v>633</v>
-      </c>
-      <c r="D85" t="s">
-        <v>228</v>
-      </c>
-      <c r="E85" t="s">
+      <c r="H85" s="2" t="s">
         <v>634</v>
-      </c>
-      <c r="F85" t="s">
-        <v>635</v>
-      </c>
-      <c r="H85" s="2" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>635</v>
+      </c>
+      <c r="B86" t="s">
+        <v>636</v>
+      </c>
+      <c r="C86" t="s">
+        <v>375</v>
+      </c>
+      <c r="D86" t="s">
+        <v>250</v>
+      </c>
+      <c r="E86" t="s">
         <v>637</v>
       </c>
-      <c r="B86" t="s">
+      <c r="F86" t="s">
         <v>638</v>
       </c>
-      <c r="C86" t="s">
-        <v>370</v>
-      </c>
-      <c r="D86" t="s">
-        <v>228</v>
-      </c>
-      <c r="E86" t="s">
+      <c r="H86" s="2" t="s">
         <v>639</v>
-      </c>
-      <c r="F86" t="s">
-        <v>640</v>
-      </c>
-      <c r="H86" s="2" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>640</v>
+      </c>
+      <c r="B87" t="s">
+        <v>101</v>
+      </c>
+      <c r="C87" t="s">
+        <v>215</v>
+      </c>
+      <c r="D87" t="s">
+        <v>228</v>
+      </c>
+      <c r="E87" t="s">
+        <v>641</v>
+      </c>
+      <c r="F87" t="s">
         <v>642</v>
       </c>
-      <c r="B87" t="s">
-        <v>346</v>
-      </c>
-      <c r="C87" t="s">
-        <v>347</v>
-      </c>
-      <c r="D87" t="s">
-        <v>245</v>
-      </c>
-      <c r="E87" t="s">
+      <c r="H87" s="2" t="s">
         <v>643</v>
-      </c>
-      <c r="F87" t="s">
-        <v>349</v>
-      </c>
-      <c r="H87" s="2" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>644</v>
+      </c>
+      <c r="B88" t="s">
         <v>645</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C88" t="s">
+        <v>215</v>
+      </c>
+      <c r="D88" t="s">
+        <v>228</v>
+      </c>
+      <c r="E88" t="s">
         <v>646</v>
       </c>
-      <c r="C88" t="s">
+      <c r="F88" t="s">
         <v>647</v>
       </c>
-      <c r="D88" t="s">
-        <v>228</v>
-      </c>
-      <c r="E88" t="s">
+      <c r="H88" s="2" t="s">
         <v>648</v>
-      </c>
-      <c r="F88" t="s">
-        <v>253</v>
-      </c>
-      <c r="H88" s="2" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>649</v>
+      </c>
+      <c r="B89" t="s">
         <v>650</v>
       </c>
-      <c r="B89" t="s">
+      <c r="C89" t="s">
         <v>651</v>
       </c>
-      <c r="C89" t="s">
+      <c r="D89" t="s">
+        <v>228</v>
+      </c>
+      <c r="E89" t="s">
         <v>652</v>
       </c>
-      <c r="D89" t="s">
-        <v>222</v>
-      </c>
-      <c r="E89" t="s">
+      <c r="F89" t="s">
         <v>653</v>
       </c>
-      <c r="F89" t="s">
+      <c r="H89" s="2" t="s">
         <v>654</v>
-      </c>
-      <c r="H89" s="2" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>655</v>
+      </c>
+      <c r="B90" t="s">
         <v>656</v>
       </c>
-      <c r="B90" t="s">
+      <c r="C90" t="s">
+        <v>315</v>
+      </c>
+      <c r="D90" t="s">
+        <v>228</v>
+      </c>
+      <c r="E90" t="s">
         <v>657</v>
       </c>
-      <c r="C90" t="s">
+      <c r="F90" t="s">
+        <v>470</v>
+      </c>
+      <c r="H90" s="2" t="s">
         <v>658</v>
-      </c>
-      <c r="D90" t="s">
-        <v>228</v>
-      </c>
-      <c r="E90" t="s">
-        <v>659</v>
-      </c>
-      <c r="F90" t="s">
-        <v>660</v>
-      </c>
-      <c r="H90" s="2" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>659</v>
+      </c>
+      <c r="B91" t="s">
+        <v>660</v>
+      </c>
+      <c r="C91" t="s">
+        <v>661</v>
+      </c>
+      <c r="D91" t="s">
+        <v>228</v>
+      </c>
+      <c r="E91" t="s">
         <v>662</v>
       </c>
-      <c r="B91" t="s">
-        <v>276</v>
-      </c>
-      <c r="C91" t="s">
+      <c r="F91" t="s">
         <v>663</v>
-      </c>
-      <c r="D91" t="s">
-        <v>228</v>
-      </c>
-      <c r="E91" t="s">
-        <v>101</v>
-      </c>
-      <c r="F91" t="s">
-        <v>278</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>664</v>
@@ -6069,381 +6213,381 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="B92" t="s">
-        <v>276</v>
+        <v>666</v>
       </c>
       <c r="C92" t="s">
-        <v>277</v>
+        <v>375</v>
       </c>
       <c r="D92" t="s">
         <v>228</v>
       </c>
       <c r="E92" t="s">
-        <v>101</v>
+        <v>667</v>
       </c>
       <c r="F92" t="s">
-        <v>278</v>
+        <v>668</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="B93" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="C93" t="s">
-        <v>668</v>
+        <v>227</v>
       </c>
       <c r="D93" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="E93" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="F93" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="B94" t="s">
-        <v>673</v>
+        <v>351</v>
       </c>
       <c r="C94" t="s">
-        <v>78</v>
+        <v>352</v>
       </c>
       <c r="D94" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="E94" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="F94" t="s">
-        <v>675</v>
+        <v>354</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B95" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C95" t="s">
-        <v>78</v>
+        <v>680</v>
       </c>
       <c r="D95" t="s">
-        <v>471</v>
+        <v>228</v>
       </c>
       <c r="E95" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="F95" t="s">
-        <v>101</v>
+        <v>258</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B96" t="s">
-        <v>259</v>
+        <v>684</v>
       </c>
       <c r="C96" t="s">
-        <v>260</v>
+        <v>685</v>
       </c>
       <c r="D96" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="E96" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="F96" t="s">
-        <v>262</v>
+        <v>687</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="B97" t="s">
-        <v>562</v>
+        <v>690</v>
       </c>
       <c r="C97" t="s">
-        <v>442</v>
+        <v>691</v>
       </c>
       <c r="D97" t="s">
         <v>228</v>
       </c>
       <c r="E97" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="F97" t="s">
-        <v>564</v>
+        <v>693</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>686</v>
+        <v>694</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
       <c r="B98" t="s">
-        <v>688</v>
+        <v>281</v>
       </c>
       <c r="C98" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="D98" t="s">
         <v>228</v>
       </c>
       <c r="E98" t="s">
-        <v>690</v>
+        <v>101</v>
       </c>
       <c r="F98" t="s">
-        <v>101</v>
+        <v>283</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="B99" t="s">
-        <v>232</v>
+        <v>281</v>
       </c>
       <c r="C99" t="s">
-        <v>693</v>
+        <v>282</v>
       </c>
       <c r="D99" t="s">
         <v>228</v>
       </c>
       <c r="E99" t="s">
-        <v>694</v>
+        <v>101</v>
       </c>
       <c r="F99" t="s">
-        <v>101</v>
+        <v>283</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>213</v>
+        <v>699</v>
       </c>
       <c r="B100" t="s">
-        <v>214</v>
+        <v>700</v>
       </c>
       <c r="C100" t="s">
-        <v>215</v>
+        <v>701</v>
       </c>
       <c r="D100" t="s">
-        <v>222</v>
+        <v>250</v>
       </c>
       <c r="E100" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="F100" t="s">
-        <v>697</v>
-      </c>
-      <c r="G100" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>213</v>
+        <v>705</v>
       </c>
       <c r="B101" t="s">
-        <v>326</v>
+        <v>706</v>
       </c>
       <c r="C101" t="s">
-        <v>215</v>
+        <v>78</v>
       </c>
       <c r="D101" t="s">
         <v>228</v>
       </c>
       <c r="E101" t="s">
-        <v>327</v>
+        <v>707</v>
       </c>
       <c r="F101" t="s">
-        <v>354</v>
+        <v>708</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>700</v>
+        <v>709</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>701</v>
+        <v>710</v>
       </c>
       <c r="B102" t="s">
-        <v>702</v>
+        <v>711</v>
       </c>
       <c r="C102" t="s">
-        <v>703</v>
+        <v>78</v>
       </c>
       <c r="D102" t="s">
-        <v>245</v>
+        <v>482</v>
       </c>
       <c r="E102" t="s">
-        <v>101</v>
+        <v>712</v>
       </c>
       <c r="F102" t="s">
         <v>101</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>704</v>
+        <v>713</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>705</v>
+        <v>714</v>
       </c>
       <c r="B103" t="s">
-        <v>298</v>
+        <v>264</v>
       </c>
       <c r="C103" t="s">
-        <v>299</v>
+        <v>265</v>
       </c>
       <c r="D103" t="s">
         <v>228</v>
       </c>
       <c r="E103" t="s">
-        <v>706</v>
+        <v>715</v>
       </c>
       <c r="F103" t="s">
-        <v>301</v>
+        <v>267</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>708</v>
+        <v>717</v>
       </c>
       <c r="B104" t="s">
-        <v>298</v>
+        <v>576</v>
       </c>
       <c r="C104" t="s">
-        <v>299</v>
+        <v>453</v>
       </c>
       <c r="D104" t="s">
         <v>228</v>
       </c>
       <c r="E104" t="s">
-        <v>709</v>
+        <v>718</v>
       </c>
       <c r="F104" t="s">
-        <v>710</v>
+        <v>578</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>711</v>
+        <v>719</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="B105" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="C105" t="s">
-        <v>370</v>
+        <v>722</v>
       </c>
       <c r="D105" t="s">
         <v>228</v>
       </c>
       <c r="E105" t="s">
-        <v>714</v>
+        <v>723</v>
       </c>
       <c r="F105" t="s">
-        <v>511</v>
+        <v>101</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>715</v>
+        <v>724</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>716</v>
+        <v>725</v>
       </c>
       <c r="B106" t="s">
-        <v>717</v>
+        <v>238</v>
       </c>
       <c r="C106" t="s">
-        <v>370</v>
+        <v>726</v>
       </c>
       <c r="D106" t="s">
         <v>228</v>
       </c>
       <c r="E106" t="s">
-        <v>718</v>
+        <v>727</v>
       </c>
       <c r="F106" t="s">
-        <v>719</v>
+        <v>101</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>720</v>
+        <v>728</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>721</v>
+        <v>213</v>
       </c>
       <c r="B107" t="s">
-        <v>722</v>
+        <v>214</v>
       </c>
       <c r="C107" t="s">
-        <v>310</v>
+        <v>215</v>
       </c>
       <c r="D107" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="E107" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="F107" t="s">
-        <v>101</v>
+        <v>730</v>
+      </c>
+      <c r="G107" t="s">
+        <v>731</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>725</v>
+        <v>213</v>
       </c>
       <c r="B108" t="s">
-        <v>726</v>
+        <v>331</v>
       </c>
       <c r="C108" t="s">
         <v>215</v>
@@ -6452,220 +6596,220 @@
         <v>228</v>
       </c>
       <c r="E108" t="s">
-        <v>727</v>
+        <v>332</v>
       </c>
       <c r="F108" t="s">
-        <v>728</v>
+        <v>359</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="B109" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="C109" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="D109" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E109" t="s">
-        <v>733</v>
+        <v>101</v>
       </c>
       <c r="F109" t="s">
         <v>101</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>730</v>
+        <v>738</v>
       </c>
       <c r="B110" t="s">
-        <v>731</v>
+        <v>303</v>
       </c>
       <c r="C110" t="s">
-        <v>735</v>
+        <v>304</v>
       </c>
       <c r="D110" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="E110" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="F110" t="s">
-        <v>101</v>
+        <v>306</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>730</v>
+        <v>741</v>
       </c>
       <c r="B111" t="s">
-        <v>731</v>
+        <v>303</v>
       </c>
       <c r="C111" t="s">
-        <v>737</v>
+        <v>304</v>
       </c>
       <c r="D111" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="E111" t="s">
-        <v>733</v>
+        <v>742</v>
       </c>
       <c r="F111" t="s">
-        <v>101</v>
+        <v>743</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>730</v>
+        <v>745</v>
       </c>
       <c r="B112" t="s">
-        <v>731</v>
+        <v>746</v>
       </c>
       <c r="C112" t="s">
-        <v>739</v>
+        <v>375</v>
       </c>
       <c r="D112" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="E112" t="s">
-        <v>733</v>
+        <v>747</v>
       </c>
       <c r="F112" t="s">
-        <v>101</v>
+        <v>522</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>740</v>
+        <v>748</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>741</v>
+        <v>749</v>
       </c>
       <c r="B113" t="s">
-        <v>742</v>
+        <v>750</v>
       </c>
       <c r="C113" t="s">
-        <v>743</v>
+        <v>375</v>
       </c>
       <c r="D113" t="s">
         <v>228</v>
       </c>
       <c r="E113" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="F113" t="s">
-        <v>101</v>
+        <v>752</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>746</v>
+        <v>754</v>
       </c>
       <c r="B114" t="s">
-        <v>747</v>
+        <v>755</v>
       </c>
       <c r="C114" t="s">
-        <v>227</v>
+        <v>315</v>
       </c>
       <c r="D114" t="s">
         <v>228</v>
       </c>
       <c r="E114" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="F114" t="s">
-        <v>749</v>
+        <v>101</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="B115" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="C115" t="s">
-        <v>522</v>
+        <v>215</v>
       </c>
       <c r="D115" t="s">
         <v>228</v>
       </c>
       <c r="E115" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="F115" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="B116" t="s">
-        <v>752</v>
+        <v>764</v>
       </c>
       <c r="C116" t="s">
-        <v>522</v>
+        <v>765</v>
       </c>
       <c r="D116" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="E116" t="s">
-        <v>757</v>
+        <v>766</v>
       </c>
       <c r="F116" t="s">
-        <v>758</v>
+        <v>101</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>759</v>
+        <v>767</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B117" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="C117" t="s">
-        <v>227</v>
+        <v>768</v>
       </c>
       <c r="D117" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="E117" t="s">
-        <v>101</v>
+        <v>766</v>
       </c>
       <c r="F117" t="s">
         <v>101</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
@@ -6676,341 +6820,571 @@
         <v>764</v>
       </c>
       <c r="C118" t="s">
-        <v>215</v>
+        <v>770</v>
       </c>
       <c r="D118" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="E118" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="F118" t="s">
-        <v>766</v>
+        <v>101</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="B119" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="C119" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="D119" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="E119" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="F119" t="s">
-        <v>253</v>
+        <v>101</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B120" t="s">
-        <v>527</v>
+        <v>775</v>
       </c>
       <c r="C120" t="s">
-        <v>528</v>
+        <v>369</v>
       </c>
       <c r="D120" t="s">
         <v>228</v>
       </c>
       <c r="E120" t="s">
-        <v>648</v>
+        <v>776</v>
       </c>
       <c r="F120" t="s">
-        <v>530</v>
+        <v>777</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="B121" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="C121" t="s">
-        <v>310</v>
+        <v>781</v>
       </c>
       <c r="D121" t="s">
         <v>228</v>
       </c>
       <c r="E121" t="s">
-        <v>777</v>
+        <v>782</v>
       </c>
       <c r="F121" t="s">
-        <v>778</v>
+        <v>101</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="B122" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="C122" t="s">
-        <v>782</v>
+        <v>234</v>
       </c>
       <c r="D122" t="s">
         <v>228</v>
       </c>
       <c r="E122" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="F122" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>780</v>
+        <v>789</v>
       </c>
       <c r="B123" t="s">
-        <v>781</v>
+        <v>790</v>
       </c>
       <c r="C123" t="s">
-        <v>786</v>
+        <v>533</v>
       </c>
       <c r="D123" t="s">
         <v>228</v>
       </c>
       <c r="E123" t="s">
-        <v>783</v>
+        <v>791</v>
       </c>
       <c r="F123" t="s">
-        <v>784</v>
+        <v>606</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>787</v>
+        <v>792</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="B124" t="s">
-        <v>421</v>
+        <v>790</v>
       </c>
       <c r="C124" t="s">
-        <v>78</v>
+        <v>533</v>
       </c>
       <c r="D124" t="s">
         <v>228</v>
       </c>
       <c r="E124" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="F124" t="s">
-        <v>423</v>
+        <v>795</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>790</v>
+        <v>796</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="B125" t="s">
-        <v>792</v>
+        <v>798</v>
       </c>
       <c r="C125" t="s">
-        <v>793</v>
+        <v>234</v>
       </c>
       <c r="D125" t="s">
         <v>228</v>
       </c>
       <c r="E125" t="s">
-        <v>794</v>
+        <v>101</v>
       </c>
       <c r="F125" t="s">
-        <v>795</v>
+        <v>101</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="B126" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C126" t="s">
-        <v>799</v>
+        <v>215</v>
       </c>
       <c r="D126" t="s">
         <v>228</v>
       </c>
       <c r="E126" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="F126" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="B127" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="C127" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="D127" t="s">
-        <v>471</v>
+        <v>228</v>
       </c>
       <c r="E127" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="F127" t="s">
-        <v>101</v>
+        <v>258</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="B128" t="s">
-        <v>804</v>
+        <v>538</v>
       </c>
       <c r="C128" t="s">
-        <v>805</v>
+        <v>539</v>
       </c>
       <c r="D128" t="s">
-        <v>471</v>
+        <v>228</v>
       </c>
       <c r="E128" t="s">
-        <v>809</v>
+        <v>681</v>
       </c>
       <c r="F128" t="s">
-        <v>101</v>
+        <v>541</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B129" t="s">
-        <v>597</v>
+        <v>813</v>
       </c>
       <c r="C129" t="s">
-        <v>215</v>
+        <v>315</v>
       </c>
       <c r="D129" t="s">
         <v>228</v>
       </c>
       <c r="E129" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="F129" t="s">
-        <v>599</v>
+        <v>815</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="B130" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="C130" t="s">
-        <v>370</v>
+        <v>819</v>
       </c>
       <c r="D130" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="E130" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="F130" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="B131" t="s">
-        <v>815</v>
+        <v>824</v>
       </c>
       <c r="C131" t="s">
-        <v>820</v>
+        <v>825</v>
       </c>
       <c r="D131" t="s">
         <v>228</v>
       </c>
       <c r="E131" t="s">
-        <v>821</v>
+        <v>826</v>
       </c>
       <c r="F131" t="s">
-        <v>817</v>
+        <v>827</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>822</v>
+        <v>828</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="B132" t="s">
-        <v>815</v>
+        <v>824</v>
       </c>
       <c r="C132" t="s">
-        <v>370</v>
+        <v>829</v>
       </c>
       <c r="D132" t="s">
         <v>228</v>
       </c>
       <c r="E132" t="s">
-        <v>816</v>
+        <v>826</v>
       </c>
       <c r="F132" t="s">
-        <v>817</v>
+        <v>827</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>823</v>
+        <v>830</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>831</v>
+      </c>
+      <c r="B133" t="s">
+        <v>426</v>
+      </c>
+      <c r="C133" t="s">
+        <v>78</v>
+      </c>
+      <c r="D133" t="s">
+        <v>228</v>
+      </c>
+      <c r="E133" t="s">
+        <v>832</v>
+      </c>
+      <c r="F133" t="s">
+        <v>428</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>834</v>
+      </c>
+      <c r="B134" t="s">
+        <v>835</v>
+      </c>
+      <c r="C134" t="s">
+        <v>836</v>
+      </c>
+      <c r="D134" t="s">
+        <v>228</v>
+      </c>
+      <c r="E134" t="s">
+        <v>837</v>
+      </c>
+      <c r="F134" t="s">
+        <v>838</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>840</v>
+      </c>
+      <c r="B135" t="s">
+        <v>841</v>
+      </c>
+      <c r="C135" t="s">
+        <v>842</v>
+      </c>
+      <c r="D135" t="s">
+        <v>228</v>
+      </c>
+      <c r="E135" t="s">
+        <v>843</v>
+      </c>
+      <c r="F135" t="s">
+        <v>844</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>846</v>
+      </c>
+      <c r="B136" t="s">
+        <v>847</v>
+      </c>
+      <c r="C136" t="s">
+        <v>848</v>
+      </c>
+      <c r="D136" t="s">
+        <v>482</v>
+      </c>
+      <c r="E136" t="s">
+        <v>849</v>
+      </c>
+      <c r="F136" t="s">
+        <v>101</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>851</v>
+      </c>
+      <c r="B137" t="s">
+        <v>847</v>
+      </c>
+      <c r="C137" t="s">
+        <v>848</v>
+      </c>
+      <c r="D137" t="s">
+        <v>482</v>
+      </c>
+      <c r="E137" t="s">
+        <v>852</v>
+      </c>
+      <c r="F137" t="s">
+        <v>101</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>854</v>
+      </c>
+      <c r="B138" t="s">
+        <v>855</v>
+      </c>
+      <c r="C138" t="s">
+        <v>856</v>
+      </c>
+      <c r="D138" t="s">
+        <v>482</v>
+      </c>
+      <c r="E138" t="s">
+        <v>857</v>
+      </c>
+      <c r="F138" t="s">
+        <v>101</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>859</v>
+      </c>
+      <c r="B139" t="s">
+        <v>623</v>
+      </c>
+      <c r="C139" t="s">
+        <v>215</v>
+      </c>
+      <c r="D139" t="s">
+        <v>228</v>
+      </c>
+      <c r="E139" t="s">
+        <v>860</v>
+      </c>
+      <c r="F139" t="s">
+        <v>625</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>862</v>
+      </c>
+      <c r="B140" t="s">
+        <v>863</v>
+      </c>
+      <c r="C140" t="s">
+        <v>375</v>
+      </c>
+      <c r="D140" t="s">
+        <v>228</v>
+      </c>
+      <c r="E140" t="s">
+        <v>864</v>
+      </c>
+      <c r="F140" t="s">
+        <v>865</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>867</v>
+      </c>
+      <c r="B141" t="s">
+        <v>863</v>
+      </c>
+      <c r="C141" t="s">
+        <v>868</v>
+      </c>
+      <c r="D141" t="s">
+        <v>228</v>
+      </c>
+      <c r="E141" t="s">
+        <v>869</v>
+      </c>
+      <c r="F141" t="s">
+        <v>865</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>867</v>
+      </c>
+      <c r="B142" t="s">
+        <v>863</v>
+      </c>
+      <c r="C142" t="s">
+        <v>375</v>
+      </c>
+      <c r="D142" t="s">
+        <v>228</v>
+      </c>
+      <c r="E142" t="s">
+        <v>864</v>
+      </c>
+      <c r="F142" t="s">
+        <v>865</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>871</v>
       </c>
     </row>
   </sheetData>
@@ -7147,6 +7521,16 @@
     <hyperlink ref="H130" r:id="rId129"/>
     <hyperlink ref="H131" r:id="rId130"/>
     <hyperlink ref="H132" r:id="rId131"/>
+    <hyperlink ref="H133" r:id="rId132"/>
+    <hyperlink ref="H134" r:id="rId133"/>
+    <hyperlink ref="H135" r:id="rId134"/>
+    <hyperlink ref="H136" r:id="rId135"/>
+    <hyperlink ref="H137" r:id="rId136"/>
+    <hyperlink ref="H138" r:id="rId137"/>
+    <hyperlink ref="H139" r:id="rId138"/>
+    <hyperlink ref="H140" r:id="rId139"/>
+    <hyperlink ref="H141" r:id="rId140"/>
+    <hyperlink ref="H142" r:id="rId141"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-08-13.xlsx
+++ b/docs/xlsx/jobs-2026-08-13.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="872">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="880">
   <si>
     <t>Title</t>
   </si>
@@ -988,6 +988,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/023e9b70db634e7a986b113685456467-communications-associate-campaign-legal-center-washington</t>
   </si>
   <si>
+    <t>Communications Director</t>
+  </si>
+  <si>
+    <t>Mount Shasta Bioregional Ecology Center</t>
+  </si>
+  <si>
+    <t>Mount Shasta, California</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Climate Change, Rural Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bd1ab0bd1bb44aa68e91df4771c06f73-communications-director-mount-shasta-bioregional-ecology-center-mount-shasta</t>
+  </si>
+  <si>
     <t>Communications Director - Building Bridges Initiative national platform</t>
   </si>
   <si>
@@ -1495,9 +1513,6 @@
     <t>USD 73000.00 - 73000.00/year</t>
   </si>
   <si>
-    <t>Environment, Climate Change, Rural Areas</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/b71f9d95c25743d4ae62ff5489810a4f-forests-fire-and-communities-senior-program-manager-washington-conservation-action-seattle</t>
   </si>
   <si>
@@ -1645,6 +1660,12 @@
     <t>https://www.idealist.org/en/nonprofit-job/e7249ab767274711b65f7edd631468fb-immigration-attorney-pt-aids-center-of-queens-county-inc-queens-county</t>
   </si>
   <si>
+    <t>AIDS Center of Queens County, Inc. - ACQC</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e7249ab767274711b65f7edd631468fb-immigration-attorney-pt-aids-center-of-queens-county-inc-acqc-queens-county</t>
+  </si>
+  <si>
     <t>Immigration Justice Project - Senior Paralegal</t>
   </si>
   <si>
@@ -2450,6 +2471,9 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/0213d7a1b90b4606ad94093b9eee2144-therapist-bilingual-lmswlcswlmhc-aids-center-of-queens-county-inc-queens-county</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0213d7a1b90b4606ad94093b9eee2144-therapist-bilingual-lmswlcswlmhc-aids-center-of-queens-county-inc-acqc-queens-county</t>
   </si>
   <si>
     <t>Toddler Teacher - Seola Gardens</t>
@@ -4102,7 +4126,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H142"/>
+  <dimension ref="A1:H145"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -4632,39 +4656,39 @@
         <v>331</v>
       </c>
       <c r="C23" t="s">
-        <v>215</v>
+        <v>332</v>
       </c>
       <c r="D23" t="s">
         <v>228</v>
       </c>
       <c r="E23" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F23" t="s">
-        <v>101</v>
+        <v>334</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B24" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C24" t="s">
-        <v>336</v>
+        <v>215</v>
       </c>
       <c r="D24" t="s">
         <v>228</v>
       </c>
       <c r="E24" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F24" t="s">
-        <v>338</v>
+        <v>101</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>339</v>
@@ -4678,59 +4702,59 @@
         <v>341</v>
       </c>
       <c r="C25" t="s">
-        <v>215</v>
+        <v>342</v>
       </c>
       <c r="D25" t="s">
         <v>228</v>
       </c>
       <c r="E25" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F25" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B26" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C26" t="s">
-        <v>347</v>
+        <v>215</v>
       </c>
       <c r="D26" t="s">
         <v>228</v>
       </c>
       <c r="E26" t="s">
-        <v>101</v>
+        <v>348</v>
       </c>
       <c r="F26" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B27" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C27" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D27" t="s">
-        <v>250</v>
+        <v>228</v>
       </c>
       <c r="E27" t="s">
-        <v>353</v>
+        <v>101</v>
       </c>
       <c r="F27" t="s">
         <v>354</v>
@@ -4747,30 +4771,30 @@
         <v>357</v>
       </c>
       <c r="C28" t="s">
-        <v>227</v>
+        <v>358</v>
       </c>
       <c r="D28" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="E28" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F28" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B29" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C29" t="s">
-        <v>363</v>
+        <v>227</v>
       </c>
       <c r="D29" t="s">
         <v>228</v>
@@ -4839,99 +4863,99 @@
         <v>380</v>
       </c>
       <c r="C32" t="s">
-        <v>234</v>
+        <v>381</v>
       </c>
       <c r="D32" t="s">
         <v>228</v>
       </c>
       <c r="E32" t="s">
-        <v>327</v>
+        <v>382</v>
       </c>
       <c r="F32" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="B33" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C33" t="s">
-        <v>384</v>
+        <v>234</v>
       </c>
       <c r="D33" t="s">
         <v>228</v>
       </c>
       <c r="E33" t="s">
-        <v>385</v>
+        <v>333</v>
       </c>
       <c r="F33" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B34" t="s">
-        <v>303</v>
+        <v>389</v>
       </c>
       <c r="C34" t="s">
-        <v>304</v>
+        <v>390</v>
       </c>
       <c r="D34" t="s">
         <v>228</v>
       </c>
       <c r="E34" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F34" t="s">
-        <v>306</v>
+        <v>392</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="B35" t="s">
-        <v>391</v>
+        <v>303</v>
       </c>
       <c r="C35" t="s">
-        <v>375</v>
+        <v>304</v>
       </c>
       <c r="D35" t="s">
         <v>228</v>
       </c>
       <c r="E35" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F35" t="s">
-        <v>393</v>
+        <v>306</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B36" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C36" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="D36" t="s">
         <v>228</v>
@@ -4963,41 +4987,41 @@
         <v>404</v>
       </c>
       <c r="F37" t="s">
-        <v>101</v>
+        <v>405</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B38" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C38" t="s">
-        <v>215</v>
+        <v>409</v>
       </c>
       <c r="D38" t="s">
         <v>228</v>
       </c>
       <c r="E38" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F38" t="s">
-        <v>409</v>
+        <v>101</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B39" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C39" t="s">
         <v>215</v>
@@ -5006,21 +5030,21 @@
         <v>228</v>
       </c>
       <c r="E39" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F39" t="s">
-        <v>101</v>
+        <v>415</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B40" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C40" t="s">
         <v>215</v>
@@ -5029,102 +5053,102 @@
         <v>228</v>
       </c>
       <c r="E40" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="F40" t="s">
-        <v>418</v>
+        <v>101</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B41" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C41" t="s">
-        <v>422</v>
+        <v>215</v>
       </c>
       <c r="D41" t="s">
         <v>228</v>
       </c>
       <c r="E41" t="s">
-        <v>239</v>
+        <v>423</v>
       </c>
       <c r="F41" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B42" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C42" t="s">
-        <v>78</v>
+        <v>428</v>
       </c>
       <c r="D42" t="s">
         <v>228</v>
       </c>
       <c r="E42" t="s">
-        <v>427</v>
+        <v>239</v>
       </c>
       <c r="F42" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B43" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C43" t="s">
-        <v>375</v>
+        <v>78</v>
       </c>
       <c r="D43" t="s">
         <v>228</v>
       </c>
       <c r="E43" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F43" t="s">
-        <v>101</v>
+        <v>434</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B44" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C44" t="s">
-        <v>436</v>
+        <v>381</v>
       </c>
       <c r="D44" t="s">
         <v>228</v>
       </c>
       <c r="E44" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F44" t="s">
-        <v>438</v>
+        <v>101</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>439</v>
@@ -5178,30 +5202,30 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="B47" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C47" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D47" t="s">
         <v>228</v>
       </c>
       <c r="E47" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F47" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="B48" t="s">
         <v>458</v>
@@ -5230,223 +5254,223 @@
         <v>464</v>
       </c>
       <c r="C49" t="s">
-        <v>215</v>
+        <v>465</v>
       </c>
       <c r="D49" t="s">
         <v>228</v>
       </c>
       <c r="E49" t="s">
-        <v>101</v>
+        <v>466</v>
       </c>
       <c r="F49" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B50" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C50" t="s">
-        <v>369</v>
+        <v>215</v>
       </c>
       <c r="D50" t="s">
         <v>228</v>
       </c>
       <c r="E50" t="s">
-        <v>469</v>
+        <v>101</v>
       </c>
       <c r="F50" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B51" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C51" t="s">
-        <v>474</v>
+        <v>375</v>
       </c>
       <c r="D51" t="s">
+        <v>228</v>
+      </c>
+      <c r="E51" t="s">
         <v>475</v>
       </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
         <v>476</v>
       </c>
-      <c r="F51" t="s">
+      <c r="H51" s="2" t="s">
         <v>477</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="B52" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="C52" t="s">
-        <v>375</v>
+        <v>480</v>
       </c>
       <c r="D52" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="E52" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="F52" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B53" t="s">
+        <v>479</v>
+      </c>
+      <c r="C53" t="s">
+        <v>381</v>
+      </c>
+      <c r="D53" t="s">
         <v>481</v>
       </c>
-      <c r="C53" t="s">
-        <v>215</v>
-      </c>
-      <c r="D53" t="s">
+      <c r="E53" t="s">
         <v>482</v>
-      </c>
-      <c r="E53" t="s">
-        <v>251</v>
       </c>
       <c r="F53" t="s">
         <v>483</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B54" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C54" t="s">
-        <v>487</v>
+        <v>215</v>
       </c>
       <c r="D54" t="s">
-        <v>228</v>
+        <v>488</v>
       </c>
       <c r="E54" t="s">
-        <v>488</v>
+        <v>251</v>
       </c>
       <c r="F54" t="s">
-        <v>101</v>
+        <v>489</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B55" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C55" t="s">
-        <v>315</v>
+        <v>493</v>
       </c>
       <c r="D55" t="s">
         <v>228</v>
       </c>
       <c r="E55" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F55" t="s">
-        <v>493</v>
+        <v>101</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B56" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C56" t="s">
-        <v>215</v>
+        <v>315</v>
       </c>
       <c r="D56" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="E56" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F56" t="s">
-        <v>258</v>
+        <v>328</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B57" t="s">
-        <v>264</v>
+        <v>501</v>
       </c>
       <c r="C57" t="s">
-        <v>500</v>
+        <v>215</v>
       </c>
       <c r="D57" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="E57" t="s">
-        <v>266</v>
+        <v>502</v>
       </c>
       <c r="F57" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B58" t="s">
-        <v>503</v>
+        <v>264</v>
       </c>
       <c r="C58" t="s">
-        <v>375</v>
+        <v>505</v>
       </c>
       <c r="D58" t="s">
         <v>228</v>
       </c>
       <c r="E58" t="s">
-        <v>504</v>
+        <v>266</v>
       </c>
       <c r="F58" t="s">
-        <v>505</v>
+        <v>267</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>506</v>
@@ -5460,56 +5484,56 @@
         <v>508</v>
       </c>
       <c r="C59" t="s">
+        <v>381</v>
+      </c>
+      <c r="D59" t="s">
+        <v>228</v>
+      </c>
+      <c r="E59" t="s">
         <v>509</v>
       </c>
-      <c r="D59" t="s">
-        <v>482</v>
-      </c>
-      <c r="E59" t="s">
+      <c r="F59" t="s">
         <v>510</v>
       </c>
-      <c r="F59" t="s">
+      <c r="H59" s="2" t="s">
         <v>511</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>512</v>
+      </c>
+      <c r="B60" t="s">
         <v>513</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" t="s">
         <v>514</v>
       </c>
-      <c r="C60" t="s">
+      <c r="D60" t="s">
+        <v>488</v>
+      </c>
+      <c r="E60" t="s">
         <v>515</v>
       </c>
-      <c r="D60" t="s">
-        <v>228</v>
-      </c>
-      <c r="E60" t="s">
+      <c r="F60" t="s">
         <v>516</v>
       </c>
-      <c r="F60" t="s">
+      <c r="H60" s="2" t="s">
         <v>517</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>518</v>
+      </c>
+      <c r="B61" t="s">
         <v>519</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C61" t="s">
         <v>520</v>
       </c>
-      <c r="C61" t="s">
-        <v>375</v>
-      </c>
       <c r="D61" t="s">
-        <v>475</v>
+        <v>228</v>
       </c>
       <c r="E61" t="s">
         <v>521</v>
@@ -5526,108 +5550,108 @@
         <v>524</v>
       </c>
       <c r="B62" t="s">
-        <v>503</v>
+        <v>525</v>
       </c>
       <c r="C62" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="D62" t="s">
-        <v>228</v>
+        <v>481</v>
       </c>
       <c r="E62" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F62" t="s">
-        <v>505</v>
+        <v>527</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B63" t="s">
-        <v>528</v>
+        <v>508</v>
       </c>
       <c r="C63" t="s">
-        <v>234</v>
+        <v>381</v>
       </c>
       <c r="D63" t="s">
         <v>228</v>
       </c>
       <c r="E63" t="s">
-        <v>342</v>
+        <v>530</v>
       </c>
       <c r="F63" t="s">
-        <v>529</v>
+        <v>510</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B64" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C64" t="s">
-        <v>533</v>
+        <v>234</v>
       </c>
       <c r="D64" t="s">
         <v>228</v>
       </c>
       <c r="E64" t="s">
+        <v>348</v>
+      </c>
+      <c r="F64" t="s">
         <v>534</v>
       </c>
-      <c r="F64" t="s">
+      <c r="H64" s="2" t="s">
         <v>535</v>
-      </c>
-      <c r="H64" s="2" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>536</v>
+      </c>
+      <c r="B65" t="s">
         <v>537</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
         <v>538</v>
       </c>
-      <c r="C65" t="s">
+      <c r="D65" t="s">
+        <v>228</v>
+      </c>
+      <c r="E65" t="s">
         <v>539</v>
       </c>
-      <c r="D65" t="s">
-        <v>250</v>
-      </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>540</v>
       </c>
-      <c r="F65" t="s">
+      <c r="H65" s="2" t="s">
         <v>541</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>542</v>
+      </c>
+      <c r="B66" t="s">
         <v>543</v>
       </c>
-      <c r="B66" t="s">
+      <c r="C66" t="s">
         <v>544</v>
       </c>
-      <c r="C66" t="s">
+      <c r="D66" t="s">
+        <v>250</v>
+      </c>
+      <c r="E66" t="s">
         <v>545</v>
-      </c>
-      <c r="D66" t="s">
-        <v>228</v>
-      </c>
-      <c r="E66" t="s">
-        <v>101</v>
       </c>
       <c r="F66" t="s">
         <v>546</v>
@@ -5638,453 +5662,453 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>542</v>
+      </c>
+      <c r="B67" t="s">
         <v>548</v>
       </c>
-      <c r="B67" t="s">
+      <c r="C67" t="s">
+        <v>544</v>
+      </c>
+      <c r="D67" t="s">
+        <v>250</v>
+      </c>
+      <c r="E67" t="s">
+        <v>545</v>
+      </c>
+      <c r="F67" t="s">
+        <v>546</v>
+      </c>
+      <c r="H67" s="2" t="s">
         <v>549</v>
-      </c>
-      <c r="C67" t="s">
-        <v>375</v>
-      </c>
-      <c r="D67" t="s">
-        <v>222</v>
-      </c>
-      <c r="E67" t="s">
-        <v>550</v>
-      </c>
-      <c r="F67" t="s">
-        <v>551</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>550</v>
+      </c>
+      <c r="B68" t="s">
+        <v>551</v>
+      </c>
+      <c r="C68" t="s">
+        <v>552</v>
+      </c>
+      <c r="D68" t="s">
+        <v>228</v>
+      </c>
+      <c r="E68" t="s">
+        <v>101</v>
+      </c>
+      <c r="F68" t="s">
         <v>553</v>
       </c>
-      <c r="B68" t="s">
+      <c r="H68" s="2" t="s">
         <v>554</v>
-      </c>
-      <c r="C68" t="s">
-        <v>375</v>
-      </c>
-      <c r="D68" t="s">
-        <v>228</v>
-      </c>
-      <c r="E68" t="s">
-        <v>510</v>
-      </c>
-      <c r="F68" t="s">
-        <v>101</v>
-      </c>
-      <c r="H68" s="2" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>555</v>
+      </c>
+      <c r="B69" t="s">
         <v>556</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69" t="s">
+        <v>381</v>
+      </c>
+      <c r="D69" t="s">
+        <v>222</v>
+      </c>
+      <c r="E69" t="s">
         <v>557</v>
       </c>
-      <c r="C69" t="s">
+      <c r="F69" t="s">
         <v>558</v>
       </c>
-      <c r="D69" t="s">
-        <v>250</v>
-      </c>
-      <c r="E69" t="s">
+      <c r="H69" s="2" t="s">
         <v>559</v>
-      </c>
-      <c r="F69" t="s">
-        <v>560</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>560</v>
+      </c>
+      <c r="B70" t="s">
+        <v>561</v>
+      </c>
+      <c r="C70" t="s">
+        <v>381</v>
+      </c>
+      <c r="D70" t="s">
+        <v>228</v>
+      </c>
+      <c r="E70" t="s">
+        <v>515</v>
+      </c>
+      <c r="F70" t="s">
+        <v>101</v>
+      </c>
+      <c r="H70" s="2" t="s">
         <v>562</v>
-      </c>
-      <c r="B70" t="s">
-        <v>503</v>
-      </c>
-      <c r="C70" t="s">
-        <v>234</v>
-      </c>
-      <c r="D70" t="s">
-        <v>228</v>
-      </c>
-      <c r="E70" t="s">
-        <v>563</v>
-      </c>
-      <c r="F70" t="s">
-        <v>505</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>563</v>
+      </c>
+      <c r="B71" t="s">
+        <v>564</v>
+      </c>
+      <c r="C71" t="s">
         <v>565</v>
       </c>
-      <c r="B71" t="s">
+      <c r="D71" t="s">
+        <v>250</v>
+      </c>
+      <c r="E71" t="s">
         <v>566</v>
       </c>
-      <c r="C71" t="s">
+      <c r="F71" t="s">
         <v>567</v>
       </c>
-      <c r="D71" t="s">
-        <v>228</v>
-      </c>
-      <c r="E71" t="s">
+      <c r="H71" s="2" t="s">
         <v>568</v>
-      </c>
-      <c r="F71" t="s">
-        <v>101</v>
-      </c>
-      <c r="H71" s="2" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>569</v>
+      </c>
+      <c r="B72" t="s">
+        <v>508</v>
+      </c>
+      <c r="C72" t="s">
+        <v>234</v>
+      </c>
+      <c r="D72" t="s">
+        <v>228</v>
+      </c>
+      <c r="E72" t="s">
         <v>570</v>
       </c>
-      <c r="B72" t="s">
+      <c r="F72" t="s">
+        <v>510</v>
+      </c>
+      <c r="H72" s="2" t="s">
         <v>571</v>
-      </c>
-      <c r="C72" t="s">
-        <v>453</v>
-      </c>
-      <c r="D72" t="s">
-        <v>228</v>
-      </c>
-      <c r="E72" t="s">
-        <v>572</v>
-      </c>
-      <c r="F72" t="s">
-        <v>573</v>
-      </c>
-      <c r="H72" s="2" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>572</v>
+      </c>
+      <c r="B73" t="s">
+        <v>573</v>
+      </c>
+      <c r="C73" t="s">
+        <v>574</v>
+      </c>
+      <c r="D73" t="s">
+        <v>228</v>
+      </c>
+      <c r="E73" t="s">
         <v>575</v>
       </c>
-      <c r="B73" t="s">
+      <c r="F73" t="s">
+        <v>101</v>
+      </c>
+      <c r="H73" s="2" t="s">
         <v>576</v>
-      </c>
-      <c r="C73" t="s">
-        <v>375</v>
-      </c>
-      <c r="D73" t="s">
-        <v>228</v>
-      </c>
-      <c r="E73" t="s">
-        <v>577</v>
-      </c>
-      <c r="F73" t="s">
-        <v>578</v>
-      </c>
-      <c r="H73" s="2" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>577</v>
+      </c>
+      <c r="B74" t="s">
+        <v>578</v>
+      </c>
+      <c r="C74" t="s">
+        <v>459</v>
+      </c>
+      <c r="D74" t="s">
+        <v>228</v>
+      </c>
+      <c r="E74" t="s">
+        <v>579</v>
+      </c>
+      <c r="F74" t="s">
         <v>580</v>
       </c>
-      <c r="B74" t="s">
-        <v>362</v>
-      </c>
-      <c r="C74" t="s">
-        <v>363</v>
-      </c>
-      <c r="D74" t="s">
-        <v>228</v>
-      </c>
-      <c r="E74" t="s">
+      <c r="H74" s="2" t="s">
         <v>581</v>
-      </c>
-      <c r="F74" t="s">
-        <v>582</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>582</v>
+      </c>
+      <c r="B75" t="s">
+        <v>583</v>
+      </c>
+      <c r="C75" t="s">
+        <v>381</v>
+      </c>
+      <c r="D75" t="s">
+        <v>228</v>
+      </c>
+      <c r="E75" t="s">
         <v>584</v>
       </c>
-      <c r="B75" t="s">
+      <c r="F75" t="s">
         <v>585</v>
       </c>
-      <c r="C75" t="s">
-        <v>453</v>
-      </c>
-      <c r="D75" t="s">
-        <v>228</v>
-      </c>
-      <c r="E75" t="s">
+      <c r="H75" s="2" t="s">
         <v>586</v>
-      </c>
-      <c r="F75" t="s">
-        <v>587</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>587</v>
+      </c>
+      <c r="B76" t="s">
+        <v>368</v>
+      </c>
+      <c r="C76" t="s">
+        <v>369</v>
+      </c>
+      <c r="D76" t="s">
+        <v>228</v>
+      </c>
+      <c r="E76" t="s">
+        <v>588</v>
+      </c>
+      <c r="F76" t="s">
         <v>589</v>
       </c>
-      <c r="B76" t="s">
+      <c r="H76" s="2" t="s">
         <v>590</v>
-      </c>
-      <c r="C76" t="s">
-        <v>215</v>
-      </c>
-      <c r="D76" t="s">
-        <v>222</v>
-      </c>
-      <c r="E76" t="s">
-        <v>591</v>
-      </c>
-      <c r="F76" t="s">
-        <v>592</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>591</v>
+      </c>
+      <c r="B77" t="s">
+        <v>592</v>
+      </c>
+      <c r="C77" t="s">
+        <v>459</v>
+      </c>
+      <c r="D77" t="s">
+        <v>228</v>
+      </c>
+      <c r="E77" t="s">
+        <v>593</v>
+      </c>
+      <c r="F77" t="s">
         <v>594</v>
       </c>
-      <c r="B77" t="s">
+      <c r="H77" s="2" t="s">
         <v>595</v>
-      </c>
-      <c r="C77" t="s">
-        <v>375</v>
-      </c>
-      <c r="D77" t="s">
-        <v>228</v>
-      </c>
-      <c r="E77" t="s">
-        <v>596</v>
-      </c>
-      <c r="F77" t="s">
-        <v>597</v>
-      </c>
-      <c r="H77" s="2" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>596</v>
+      </c>
+      <c r="B78" t="s">
+        <v>597</v>
+      </c>
+      <c r="C78" t="s">
+        <v>215</v>
+      </c>
+      <c r="D78" t="s">
+        <v>222</v>
+      </c>
+      <c r="E78" t="s">
+        <v>598</v>
+      </c>
+      <c r="F78" t="s">
         <v>599</v>
       </c>
-      <c r="B78" t="s">
-        <v>426</v>
-      </c>
-      <c r="C78" t="s">
-        <v>78</v>
-      </c>
-      <c r="D78" t="s">
-        <v>228</v>
-      </c>
-      <c r="E78" t="s">
+      <c r="H78" s="2" t="s">
         <v>600</v>
-      </c>
-      <c r="F78" t="s">
-        <v>428</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>601</v>
+      </c>
+      <c r="B79" t="s">
         <v>602</v>
       </c>
-      <c r="B79" t="s">
+      <c r="C79" t="s">
+        <v>381</v>
+      </c>
+      <c r="D79" t="s">
+        <v>228</v>
+      </c>
+      <c r="E79" t="s">
         <v>603</v>
       </c>
-      <c r="C79" t="s">
+      <c r="F79" t="s">
         <v>604</v>
       </c>
-      <c r="D79" t="s">
-        <v>228</v>
-      </c>
-      <c r="E79" t="s">
+      <c r="H79" s="2" t="s">
         <v>605</v>
-      </c>
-      <c r="F79" t="s">
-        <v>606</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>606</v>
+      </c>
+      <c r="B80" t="s">
+        <v>432</v>
+      </c>
+      <c r="C80" t="s">
+        <v>78</v>
+      </c>
+      <c r="D80" t="s">
+        <v>228</v>
+      </c>
+      <c r="E80" t="s">
+        <v>607</v>
+      </c>
+      <c r="F80" t="s">
+        <v>434</v>
+      </c>
+      <c r="H80" s="2" t="s">
         <v>608</v>
-      </c>
-      <c r="B80" t="s">
-        <v>609</v>
-      </c>
-      <c r="C80" t="s">
-        <v>215</v>
-      </c>
-      <c r="D80" t="s">
-        <v>228</v>
-      </c>
-      <c r="E80" t="s">
-        <v>610</v>
-      </c>
-      <c r="F80" t="s">
-        <v>258</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>609</v>
+      </c>
+      <c r="B81" t="s">
+        <v>610</v>
+      </c>
+      <c r="C81" t="s">
+        <v>611</v>
+      </c>
+      <c r="D81" t="s">
+        <v>228</v>
+      </c>
+      <c r="E81" t="s">
         <v>612</v>
       </c>
-      <c r="B81" t="s">
+      <c r="F81" t="s">
         <v>613</v>
       </c>
-      <c r="C81" t="s">
+      <c r="H81" s="2" t="s">
         <v>614</v>
-      </c>
-      <c r="D81" t="s">
-        <v>228</v>
-      </c>
-      <c r="E81" t="s">
-        <v>615</v>
-      </c>
-      <c r="F81" t="s">
-        <v>616</v>
-      </c>
-      <c r="H81" s="2" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>615</v>
+      </c>
+      <c r="B82" t="s">
+        <v>616</v>
+      </c>
+      <c r="C82" t="s">
+        <v>215</v>
+      </c>
+      <c r="D82" t="s">
+        <v>228</v>
+      </c>
+      <c r="E82" t="s">
+        <v>617</v>
+      </c>
+      <c r="F82" t="s">
+        <v>258</v>
+      </c>
+      <c r="H82" s="2" t="s">
         <v>618</v>
-      </c>
-      <c r="B82" t="s">
-        <v>619</v>
-      </c>
-      <c r="C82" t="s">
-        <v>539</v>
-      </c>
-      <c r="D82" t="s">
-        <v>228</v>
-      </c>
-      <c r="E82" t="s">
-        <v>620</v>
-      </c>
-      <c r="F82" t="s">
-        <v>101</v>
-      </c>
-      <c r="H82" s="2" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>619</v>
+      </c>
+      <c r="B83" t="s">
+        <v>620</v>
+      </c>
+      <c r="C83" t="s">
+        <v>621</v>
+      </c>
+      <c r="D83" t="s">
+        <v>228</v>
+      </c>
+      <c r="E83" t="s">
         <v>622</v>
       </c>
-      <c r="B83" t="s">
+      <c r="F83" t="s">
         <v>623</v>
       </c>
-      <c r="C83" t="s">
-        <v>215</v>
-      </c>
-      <c r="D83" t="s">
-        <v>228</v>
-      </c>
-      <c r="E83" t="s">
+      <c r="H83" s="2" t="s">
         <v>624</v>
-      </c>
-      <c r="F83" t="s">
-        <v>625</v>
-      </c>
-      <c r="H83" s="2" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>625</v>
+      </c>
+      <c r="B84" t="s">
+        <v>626</v>
+      </c>
+      <c r="C84" t="s">
+        <v>544</v>
+      </c>
+      <c r="D84" t="s">
+        <v>228</v>
+      </c>
+      <c r="E84" t="s">
         <v>627</v>
       </c>
-      <c r="B84" t="s">
+      <c r="F84" t="s">
+        <v>101</v>
+      </c>
+      <c r="H84" s="2" t="s">
         <v>628</v>
-      </c>
-      <c r="C84" t="s">
-        <v>629</v>
-      </c>
-      <c r="D84" t="s">
-        <v>228</v>
-      </c>
-      <c r="E84" t="s">
-        <v>630</v>
-      </c>
-      <c r="F84" t="s">
-        <v>631</v>
-      </c>
-      <c r="H84" s="2" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>629</v>
+      </c>
+      <c r="B85" t="s">
+        <v>630</v>
+      </c>
+      <c r="C85" t="s">
+        <v>215</v>
+      </c>
+      <c r="D85" t="s">
+        <v>228</v>
+      </c>
+      <c r="E85" t="s">
+        <v>631</v>
+      </c>
+      <c r="F85" t="s">
+        <v>632</v>
+      </c>
+      <c r="H85" s="2" t="s">
         <v>633</v>
-      </c>
-      <c r="B85" t="s">
-        <v>628</v>
-      </c>
-      <c r="C85" t="s">
-        <v>629</v>
-      </c>
-      <c r="D85" t="s">
-        <v>228</v>
-      </c>
-      <c r="E85" t="s">
-        <v>630</v>
-      </c>
-      <c r="F85" t="s">
-        <v>631</v>
-      </c>
-      <c r="H85" s="2" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>634</v>
+      </c>
+      <c r="B86" t="s">
         <v>635</v>
       </c>
-      <c r="B86" t="s">
+      <c r="C86" t="s">
         <v>636</v>
       </c>
-      <c r="C86" t="s">
-        <v>375</v>
-      </c>
       <c r="D86" t="s">
-        <v>250</v>
+        <v>228</v>
       </c>
       <c r="E86" t="s">
         <v>637</v>
@@ -6101,318 +6125,318 @@
         <v>640</v>
       </c>
       <c r="B87" t="s">
-        <v>101</v>
+        <v>635</v>
       </c>
       <c r="C87" t="s">
-        <v>215</v>
+        <v>636</v>
       </c>
       <c r="D87" t="s">
         <v>228</v>
       </c>
       <c r="E87" t="s">
+        <v>637</v>
+      </c>
+      <c r="F87" t="s">
+        <v>638</v>
+      </c>
+      <c r="H87" s="2" t="s">
         <v>641</v>
-      </c>
-      <c r="F87" t="s">
-        <v>642</v>
-      </c>
-      <c r="H87" s="2" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>642</v>
+      </c>
+      <c r="B88" t="s">
+        <v>643</v>
+      </c>
+      <c r="C88" t="s">
+        <v>381</v>
+      </c>
+      <c r="D88" t="s">
+        <v>250</v>
+      </c>
+      <c r="E88" t="s">
         <v>644</v>
       </c>
-      <c r="B88" t="s">
+      <c r="F88" t="s">
         <v>645</v>
       </c>
-      <c r="C88" t="s">
-        <v>215</v>
-      </c>
-      <c r="D88" t="s">
-        <v>228</v>
-      </c>
-      <c r="E88" t="s">
+      <c r="H88" s="2" t="s">
         <v>646</v>
-      </c>
-      <c r="F88" t="s">
-        <v>647</v>
-      </c>
-      <c r="H88" s="2" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>647</v>
+      </c>
+      <c r="B89" t="s">
+        <v>101</v>
+      </c>
+      <c r="C89" t="s">
+        <v>215</v>
+      </c>
+      <c r="D89" t="s">
+        <v>228</v>
+      </c>
+      <c r="E89" t="s">
+        <v>648</v>
+      </c>
+      <c r="F89" t="s">
         <v>649</v>
       </c>
-      <c r="B89" t="s">
+      <c r="H89" s="2" t="s">
         <v>650</v>
-      </c>
-      <c r="C89" t="s">
-        <v>651</v>
-      </c>
-      <c r="D89" t="s">
-        <v>228</v>
-      </c>
-      <c r="E89" t="s">
-        <v>652</v>
-      </c>
-      <c r="F89" t="s">
-        <v>653</v>
-      </c>
-      <c r="H89" s="2" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>651</v>
+      </c>
+      <c r="B90" t="s">
+        <v>652</v>
+      </c>
+      <c r="C90" t="s">
+        <v>215</v>
+      </c>
+      <c r="D90" t="s">
+        <v>228</v>
+      </c>
+      <c r="E90" t="s">
+        <v>653</v>
+      </c>
+      <c r="F90" t="s">
+        <v>654</v>
+      </c>
+      <c r="H90" s="2" t="s">
         <v>655</v>
-      </c>
-      <c r="B90" t="s">
-        <v>656</v>
-      </c>
-      <c r="C90" t="s">
-        <v>315</v>
-      </c>
-      <c r="D90" t="s">
-        <v>228</v>
-      </c>
-      <c r="E90" t="s">
-        <v>657</v>
-      </c>
-      <c r="F90" t="s">
-        <v>470</v>
-      </c>
-      <c r="H90" s="2" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>656</v>
+      </c>
+      <c r="B91" t="s">
+        <v>657</v>
+      </c>
+      <c r="C91" t="s">
+        <v>658</v>
+      </c>
+      <c r="D91" t="s">
+        <v>228</v>
+      </c>
+      <c r="E91" t="s">
         <v>659</v>
       </c>
-      <c r="B91" t="s">
+      <c r="F91" t="s">
         <v>660</v>
       </c>
-      <c r="C91" t="s">
+      <c r="H91" s="2" t="s">
         <v>661</v>
-      </c>
-      <c r="D91" t="s">
-        <v>228</v>
-      </c>
-      <c r="E91" t="s">
-        <v>662</v>
-      </c>
-      <c r="F91" t="s">
-        <v>663</v>
-      </c>
-      <c r="H91" s="2" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>662</v>
+      </c>
+      <c r="B92" t="s">
+        <v>663</v>
+      </c>
+      <c r="C92" t="s">
+        <v>315</v>
+      </c>
+      <c r="D92" t="s">
+        <v>228</v>
+      </c>
+      <c r="E92" t="s">
+        <v>664</v>
+      </c>
+      <c r="F92" t="s">
+        <v>476</v>
+      </c>
+      <c r="H92" s="2" t="s">
         <v>665</v>
-      </c>
-      <c r="B92" t="s">
-        <v>666</v>
-      </c>
-      <c r="C92" t="s">
-        <v>375</v>
-      </c>
-      <c r="D92" t="s">
-        <v>228</v>
-      </c>
-      <c r="E92" t="s">
-        <v>667</v>
-      </c>
-      <c r="F92" t="s">
-        <v>668</v>
-      </c>
-      <c r="H92" s="2" t="s">
-        <v>669</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>666</v>
+      </c>
+      <c r="B93" t="s">
+        <v>667</v>
+      </c>
+      <c r="C93" t="s">
+        <v>668</v>
+      </c>
+      <c r="D93" t="s">
+        <v>228</v>
+      </c>
+      <c r="E93" t="s">
+        <v>669</v>
+      </c>
+      <c r="F93" t="s">
         <v>670</v>
       </c>
-      <c r="B93" t="s">
+      <c r="H93" s="2" t="s">
         <v>671</v>
-      </c>
-      <c r="C93" t="s">
-        <v>227</v>
-      </c>
-      <c r="D93" t="s">
-        <v>228</v>
-      </c>
-      <c r="E93" t="s">
-        <v>672</v>
-      </c>
-      <c r="F93" t="s">
-        <v>673</v>
-      </c>
-      <c r="H93" s="2" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>672</v>
+      </c>
+      <c r="B94" t="s">
+        <v>673</v>
+      </c>
+      <c r="C94" t="s">
+        <v>381</v>
+      </c>
+      <c r="D94" t="s">
+        <v>228</v>
+      </c>
+      <c r="E94" t="s">
+        <v>674</v>
+      </c>
+      <c r="F94" t="s">
         <v>675</v>
       </c>
-      <c r="B94" t="s">
-        <v>351</v>
-      </c>
-      <c r="C94" t="s">
-        <v>352</v>
-      </c>
-      <c r="D94" t="s">
-        <v>250</v>
-      </c>
-      <c r="E94" t="s">
+      <c r="H94" s="2" t="s">
         <v>676</v>
-      </c>
-      <c r="F94" t="s">
-        <v>354</v>
-      </c>
-      <c r="H94" s="2" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>677</v>
+      </c>
+      <c r="B95" t="s">
         <v>678</v>
       </c>
-      <c r="B95" t="s">
+      <c r="C95" t="s">
+        <v>227</v>
+      </c>
+      <c r="D95" t="s">
+        <v>228</v>
+      </c>
+      <c r="E95" t="s">
         <v>679</v>
       </c>
-      <c r="C95" t="s">
+      <c r="F95" t="s">
         <v>680</v>
       </c>
-      <c r="D95" t="s">
-        <v>228</v>
-      </c>
-      <c r="E95" t="s">
+      <c r="H95" s="2" t="s">
         <v>681</v>
-      </c>
-      <c r="F95" t="s">
-        <v>258</v>
-      </c>
-      <c r="H95" s="2" t="s">
-        <v>682</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>682</v>
+      </c>
+      <c r="B96" t="s">
+        <v>357</v>
+      </c>
+      <c r="C96" t="s">
+        <v>358</v>
+      </c>
+      <c r="D96" t="s">
+        <v>250</v>
+      </c>
+      <c r="E96" t="s">
         <v>683</v>
       </c>
-      <c r="B96" t="s">
+      <c r="F96" t="s">
+        <v>360</v>
+      </c>
+      <c r="H96" s="2" t="s">
         <v>684</v>
-      </c>
-      <c r="C96" t="s">
-        <v>685</v>
-      </c>
-      <c r="D96" t="s">
-        <v>222</v>
-      </c>
-      <c r="E96" t="s">
-        <v>686</v>
-      </c>
-      <c r="F96" t="s">
-        <v>687</v>
-      </c>
-      <c r="H96" s="2" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>685</v>
+      </c>
+      <c r="B97" t="s">
+        <v>686</v>
+      </c>
+      <c r="C97" t="s">
+        <v>687</v>
+      </c>
+      <c r="D97" t="s">
+        <v>228</v>
+      </c>
+      <c r="E97" t="s">
+        <v>688</v>
+      </c>
+      <c r="F97" t="s">
+        <v>258</v>
+      </c>
+      <c r="H97" s="2" t="s">
         <v>689</v>
-      </c>
-      <c r="B97" t="s">
-        <v>690</v>
-      </c>
-      <c r="C97" t="s">
-        <v>691</v>
-      </c>
-      <c r="D97" t="s">
-        <v>228</v>
-      </c>
-      <c r="E97" t="s">
-        <v>692</v>
-      </c>
-      <c r="F97" t="s">
-        <v>693</v>
-      </c>
-      <c r="H97" s="2" t="s">
-        <v>694</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>690</v>
+      </c>
+      <c r="B98" t="s">
+        <v>691</v>
+      </c>
+      <c r="C98" t="s">
+        <v>692</v>
+      </c>
+      <c r="D98" t="s">
+        <v>222</v>
+      </c>
+      <c r="E98" t="s">
+        <v>693</v>
+      </c>
+      <c r="F98" t="s">
+        <v>694</v>
+      </c>
+      <c r="H98" s="2" t="s">
         <v>695</v>
-      </c>
-      <c r="B98" t="s">
-        <v>281</v>
-      </c>
-      <c r="C98" t="s">
-        <v>696</v>
-      </c>
-      <c r="D98" t="s">
-        <v>228</v>
-      </c>
-      <c r="E98" t="s">
-        <v>101</v>
-      </c>
-      <c r="F98" t="s">
-        <v>283</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>697</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B99" t="s">
-        <v>281</v>
+        <v>697</v>
       </c>
       <c r="C99" t="s">
-        <v>282</v>
+        <v>698</v>
       </c>
       <c r="D99" t="s">
         <v>228</v>
       </c>
       <c r="E99" t="s">
-        <v>101</v>
+        <v>699</v>
       </c>
       <c r="F99" t="s">
-        <v>283</v>
+        <v>700</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="B100" t="s">
-        <v>700</v>
+        <v>281</v>
       </c>
       <c r="C100" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="D100" t="s">
-        <v>250</v>
+        <v>228</v>
       </c>
       <c r="E100" t="s">
-        <v>702</v>
+        <v>101</v>
       </c>
       <c r="F100" t="s">
-        <v>703</v>
+        <v>283</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>704</v>
@@ -6420,68 +6444,68 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>702</v>
+      </c>
+      <c r="B101" t="s">
+        <v>281</v>
+      </c>
+      <c r="C101" t="s">
+        <v>282</v>
+      </c>
+      <c r="D101" t="s">
+        <v>228</v>
+      </c>
+      <c r="E101" t="s">
+        <v>101</v>
+      </c>
+      <c r="F101" t="s">
+        <v>283</v>
+      </c>
+      <c r="H101" s="2" t="s">
         <v>705</v>
-      </c>
-      <c r="B101" t="s">
-        <v>706</v>
-      </c>
-      <c r="C101" t="s">
-        <v>78</v>
-      </c>
-      <c r="D101" t="s">
-        <v>228</v>
-      </c>
-      <c r="E101" t="s">
-        <v>707</v>
-      </c>
-      <c r="F101" t="s">
-        <v>708</v>
-      </c>
-      <c r="H101" s="2" t="s">
-        <v>709</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>706</v>
+      </c>
+      <c r="B102" t="s">
+        <v>707</v>
+      </c>
+      <c r="C102" t="s">
+        <v>708</v>
+      </c>
+      <c r="D102" t="s">
+        <v>250</v>
+      </c>
+      <c r="E102" t="s">
+        <v>709</v>
+      </c>
+      <c r="F102" t="s">
         <v>710</v>
       </c>
-      <c r="B102" t="s">
+      <c r="H102" s="2" t="s">
         <v>711</v>
-      </c>
-      <c r="C102" t="s">
-        <v>78</v>
-      </c>
-      <c r="D102" t="s">
-        <v>482</v>
-      </c>
-      <c r="E102" t="s">
-        <v>712</v>
-      </c>
-      <c r="F102" t="s">
-        <v>101</v>
-      </c>
-      <c r="H102" s="2" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>712</v>
+      </c>
+      <c r="B103" t="s">
+        <v>713</v>
+      </c>
+      <c r="C103" t="s">
+        <v>78</v>
+      </c>
+      <c r="D103" t="s">
+        <v>228</v>
+      </c>
+      <c r="E103" t="s">
         <v>714</v>
       </c>
-      <c r="B103" t="s">
-        <v>264</v>
-      </c>
-      <c r="C103" t="s">
-        <v>265</v>
-      </c>
-      <c r="D103" t="s">
-        <v>228</v>
-      </c>
-      <c r="E103" t="s">
+      <c r="F103" t="s">
         <v>715</v>
-      </c>
-      <c r="F103" t="s">
-        <v>267</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>716</v>
@@ -6492,160 +6516,160 @@
         <v>717</v>
       </c>
       <c r="B104" t="s">
-        <v>576</v>
+        <v>718</v>
       </c>
       <c r="C104" t="s">
-        <v>453</v>
+        <v>78</v>
       </c>
       <c r="D104" t="s">
-        <v>228</v>
+        <v>488</v>
       </c>
       <c r="E104" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="F104" t="s">
-        <v>578</v>
+        <v>101</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B105" t="s">
-        <v>721</v>
+        <v>264</v>
       </c>
       <c r="C105" t="s">
+        <v>265</v>
+      </c>
+      <c r="D105" t="s">
+        <v>228</v>
+      </c>
+      <c r="E105" t="s">
         <v>722</v>
       </c>
-      <c r="D105" t="s">
-        <v>228</v>
-      </c>
-      <c r="E105" t="s">
+      <c r="F105" t="s">
+        <v>267</v>
+      </c>
+      <c r="H105" s="2" t="s">
         <v>723</v>
-      </c>
-      <c r="F105" t="s">
-        <v>101</v>
-      </c>
-      <c r="H105" s="2" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
+        <v>724</v>
+      </c>
+      <c r="B106" t="s">
+        <v>583</v>
+      </c>
+      <c r="C106" t="s">
+        <v>459</v>
+      </c>
+      <c r="D106" t="s">
+        <v>228</v>
+      </c>
+      <c r="E106" t="s">
         <v>725</v>
       </c>
-      <c r="B106" t="s">
-        <v>238</v>
-      </c>
-      <c r="C106" t="s">
+      <c r="F106" t="s">
+        <v>585</v>
+      </c>
+      <c r="H106" s="2" t="s">
         <v>726</v>
-      </c>
-      <c r="D106" t="s">
-        <v>228</v>
-      </c>
-      <c r="E106" t="s">
-        <v>727</v>
-      </c>
-      <c r="F106" t="s">
-        <v>101</v>
-      </c>
-      <c r="H106" s="2" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>213</v>
+        <v>727</v>
       </c>
       <c r="B107" t="s">
-        <v>214</v>
+        <v>728</v>
       </c>
       <c r="C107" t="s">
-        <v>215</v>
+        <v>729</v>
       </c>
       <c r="D107" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="E107" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="F107" t="s">
-        <v>730</v>
-      </c>
-      <c r="G107" t="s">
+        <v>101</v>
+      </c>
+      <c r="H107" s="2" t="s">
         <v>731</v>
-      </c>
-      <c r="H107" s="2" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>213</v>
+        <v>732</v>
       </c>
       <c r="B108" t="s">
-        <v>331</v>
+        <v>238</v>
       </c>
       <c r="C108" t="s">
-        <v>215</v>
+        <v>733</v>
       </c>
       <c r="D108" t="s">
         <v>228</v>
       </c>
       <c r="E108" t="s">
-        <v>332</v>
+        <v>734</v>
       </c>
       <c r="F108" t="s">
-        <v>359</v>
+        <v>101</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>734</v>
+        <v>213</v>
       </c>
       <c r="B109" t="s">
-        <v>735</v>
+        <v>214</v>
       </c>
       <c r="C109" t="s">
+        <v>215</v>
+      </c>
+      <c r="D109" t="s">
+        <v>222</v>
+      </c>
+      <c r="E109" t="s">
         <v>736</v>
       </c>
-      <c r="D109" t="s">
-        <v>250</v>
-      </c>
-      <c r="E109" t="s">
-        <v>101</v>
-      </c>
       <c r="F109" t="s">
-        <v>101</v>
+        <v>737</v>
+      </c>
+      <c r="G109" t="s">
+        <v>738</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>738</v>
+        <v>213</v>
       </c>
       <c r="B110" t="s">
-        <v>303</v>
+        <v>337</v>
       </c>
       <c r="C110" t="s">
-        <v>304</v>
+        <v>215</v>
       </c>
       <c r="D110" t="s">
         <v>228</v>
       </c>
       <c r="E110" t="s">
-        <v>739</v>
+        <v>338</v>
       </c>
       <c r="F110" t="s">
-        <v>306</v>
+        <v>365</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>740</v>
@@ -6656,19 +6680,19 @@
         <v>741</v>
       </c>
       <c r="B111" t="s">
-        <v>303</v>
+        <v>742</v>
       </c>
       <c r="C111" t="s">
-        <v>304</v>
+        <v>743</v>
       </c>
       <c r="D111" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="E111" t="s">
-        <v>742</v>
+        <v>101</v>
       </c>
       <c r="F111" t="s">
-        <v>743</v>
+        <v>101</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>744</v>
@@ -6679,134 +6703,134 @@
         <v>745</v>
       </c>
       <c r="B112" t="s">
+        <v>303</v>
+      </c>
+      <c r="C112" t="s">
+        <v>304</v>
+      </c>
+      <c r="D112" t="s">
+        <v>228</v>
+      </c>
+      <c r="E112" t="s">
         <v>746</v>
       </c>
-      <c r="C112" t="s">
-        <v>375</v>
-      </c>
-      <c r="D112" t="s">
-        <v>228</v>
-      </c>
-      <c r="E112" t="s">
+      <c r="F112" t="s">
+        <v>306</v>
+      </c>
+      <c r="H112" s="2" t="s">
         <v>747</v>
-      </c>
-      <c r="F112" t="s">
-        <v>522</v>
-      </c>
-      <c r="H112" s="2" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
+        <v>748</v>
+      </c>
+      <c r="B113" t="s">
+        <v>303</v>
+      </c>
+      <c r="C113" t="s">
+        <v>304</v>
+      </c>
+      <c r="D113" t="s">
+        <v>228</v>
+      </c>
+      <c r="E113" t="s">
         <v>749</v>
       </c>
-      <c r="B113" t="s">
+      <c r="F113" t="s">
         <v>750</v>
       </c>
-      <c r="C113" t="s">
-        <v>375</v>
-      </c>
-      <c r="D113" t="s">
-        <v>228</v>
-      </c>
-      <c r="E113" t="s">
+      <c r="H113" s="2" t="s">
         <v>751</v>
-      </c>
-      <c r="F113" t="s">
-        <v>752</v>
-      </c>
-      <c r="H113" s="2" t="s">
-        <v>753</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>752</v>
+      </c>
+      <c r="B114" t="s">
+        <v>753</v>
+      </c>
+      <c r="C114" t="s">
+        <v>381</v>
+      </c>
+      <c r="D114" t="s">
+        <v>228</v>
+      </c>
+      <c r="E114" t="s">
         <v>754</v>
       </c>
-      <c r="B114" t="s">
+      <c r="F114" t="s">
+        <v>527</v>
+      </c>
+      <c r="H114" s="2" t="s">
         <v>755</v>
-      </c>
-      <c r="C114" t="s">
-        <v>315</v>
-      </c>
-      <c r="D114" t="s">
-        <v>228</v>
-      </c>
-      <c r="E114" t="s">
-        <v>756</v>
-      </c>
-      <c r="F114" t="s">
-        <v>101</v>
-      </c>
-      <c r="H114" s="2" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>756</v>
+      </c>
+      <c r="B115" t="s">
+        <v>757</v>
+      </c>
+      <c r="C115" t="s">
+        <v>381</v>
+      </c>
+      <c r="D115" t="s">
+        <v>228</v>
+      </c>
+      <c r="E115" t="s">
         <v>758</v>
       </c>
-      <c r="B115" t="s">
+      <c r="F115" t="s">
         <v>759</v>
       </c>
-      <c r="C115" t="s">
-        <v>215</v>
-      </c>
-      <c r="D115" t="s">
-        <v>228</v>
-      </c>
-      <c r="E115" t="s">
+      <c r="H115" s="2" t="s">
         <v>760</v>
-      </c>
-      <c r="F115" t="s">
-        <v>761</v>
-      </c>
-      <c r="H115" s="2" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>761</v>
+      </c>
+      <c r="B116" t="s">
+        <v>762</v>
+      </c>
+      <c r="C116" t="s">
+        <v>315</v>
+      </c>
+      <c r="D116" t="s">
+        <v>228</v>
+      </c>
+      <c r="E116" t="s">
         <v>763</v>
-      </c>
-      <c r="B116" t="s">
-        <v>764</v>
-      </c>
-      <c r="C116" t="s">
-        <v>765</v>
-      </c>
-      <c r="D116" t="s">
-        <v>250</v>
-      </c>
-      <c r="E116" t="s">
-        <v>766</v>
       </c>
       <c r="F116" t="s">
         <v>101</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="B117" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C117" t="s">
+        <v>215</v>
+      </c>
+      <c r="D117" t="s">
+        <v>228</v>
+      </c>
+      <c r="E117" t="s">
+        <v>767</v>
+      </c>
+      <c r="F117" t="s">
         <v>768</v>
-      </c>
-      <c r="D117" t="s">
-        <v>250</v>
-      </c>
-      <c r="E117" t="s">
-        <v>766</v>
-      </c>
-      <c r="F117" t="s">
-        <v>101</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>769</v>
@@ -6814,68 +6838,68 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="B118" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="C118" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="D118" t="s">
         <v>250</v>
       </c>
       <c r="E118" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="F118" t="s">
         <v>101</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="B119" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="C119" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="D119" t="s">
         <v>250</v>
       </c>
       <c r="E119" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="F119" t="s">
         <v>101</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="B120" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="C120" t="s">
-        <v>369</v>
+        <v>777</v>
       </c>
       <c r="D120" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="E120" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="F120" t="s">
-        <v>777</v>
+        <v>101</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>778</v>
@@ -6883,114 +6907,114 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>770</v>
+      </c>
+      <c r="B121" t="s">
+        <v>771</v>
+      </c>
+      <c r="C121" t="s">
         <v>779</v>
       </c>
-      <c r="B121" t="s">
-        <v>780</v>
-      </c>
-      <c r="C121" t="s">
-        <v>781</v>
-      </c>
       <c r="D121" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="E121" t="s">
-        <v>782</v>
+        <v>773</v>
       </c>
       <c r="F121" t="s">
         <v>101</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>781</v>
+      </c>
+      <c r="B122" t="s">
+        <v>782</v>
+      </c>
+      <c r="C122" t="s">
+        <v>375</v>
+      </c>
+      <c r="D122" t="s">
+        <v>228</v>
+      </c>
+      <c r="E122" t="s">
+        <v>783</v>
+      </c>
+      <c r="F122" t="s">
         <v>784</v>
       </c>
-      <c r="B122" t="s">
+      <c r="H122" s="2" t="s">
         <v>785</v>
-      </c>
-      <c r="C122" t="s">
-        <v>234</v>
-      </c>
-      <c r="D122" t="s">
-        <v>228</v>
-      </c>
-      <c r="E122" t="s">
-        <v>786</v>
-      </c>
-      <c r="F122" t="s">
-        <v>787</v>
-      </c>
-      <c r="H122" s="2" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
+        <v>786</v>
+      </c>
+      <c r="B123" t="s">
+        <v>787</v>
+      </c>
+      <c r="C123" t="s">
+        <v>788</v>
+      </c>
+      <c r="D123" t="s">
+        <v>228</v>
+      </c>
+      <c r="E123" t="s">
         <v>789</v>
       </c>
-      <c r="B123" t="s">
+      <c r="F123" t="s">
+        <v>101</v>
+      </c>
+      <c r="H123" s="2" t="s">
         <v>790</v>
-      </c>
-      <c r="C123" t="s">
-        <v>533</v>
-      </c>
-      <c r="D123" t="s">
-        <v>228</v>
-      </c>
-      <c r="E123" t="s">
-        <v>791</v>
-      </c>
-      <c r="F123" t="s">
-        <v>606</v>
-      </c>
-      <c r="H123" s="2" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>791</v>
+      </c>
+      <c r="B124" t="s">
+        <v>792</v>
+      </c>
+      <c r="C124" t="s">
+        <v>234</v>
+      </c>
+      <c r="D124" t="s">
+        <v>228</v>
+      </c>
+      <c r="E124" t="s">
         <v>793</v>
       </c>
-      <c r="B124" t="s">
-        <v>790</v>
-      </c>
-      <c r="C124" t="s">
-        <v>533</v>
-      </c>
-      <c r="D124" t="s">
-        <v>228</v>
-      </c>
-      <c r="E124" t="s">
+      <c r="F124" t="s">
         <v>794</v>
       </c>
-      <c r="F124" t="s">
+      <c r="H124" s="2" t="s">
         <v>795</v>
-      </c>
-      <c r="H124" s="2" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
+        <v>796</v>
+      </c>
+      <c r="B125" t="s">
         <v>797</v>
       </c>
-      <c r="B125" t="s">
+      <c r="C125" t="s">
+        <v>538</v>
+      </c>
+      <c r="D125" t="s">
+        <v>228</v>
+      </c>
+      <c r="E125" t="s">
         <v>798</v>
       </c>
-      <c r="C125" t="s">
-        <v>234</v>
-      </c>
-      <c r="D125" t="s">
-        <v>228</v>
-      </c>
-      <c r="E125" t="s">
-        <v>101</v>
-      </c>
       <c r="F125" t="s">
-        <v>101</v>
+        <v>613</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>799</v>
@@ -7001,65 +7025,65 @@
         <v>800</v>
       </c>
       <c r="B126" t="s">
+        <v>797</v>
+      </c>
+      <c r="C126" t="s">
+        <v>538</v>
+      </c>
+      <c r="D126" t="s">
+        <v>228</v>
+      </c>
+      <c r="E126" t="s">
         <v>801</v>
       </c>
-      <c r="C126" t="s">
-        <v>215</v>
-      </c>
-      <c r="D126" t="s">
-        <v>228</v>
-      </c>
-      <c r="E126" t="s">
+      <c r="F126" t="s">
         <v>802</v>
       </c>
-      <c r="F126" t="s">
+      <c r="H126" s="2" t="s">
         <v>803</v>
-      </c>
-      <c r="H126" s="2" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
+        <v>804</v>
+      </c>
+      <c r="B127" t="s">
         <v>805</v>
       </c>
-      <c r="B127" t="s">
+      <c r="C127" t="s">
+        <v>234</v>
+      </c>
+      <c r="D127" t="s">
+        <v>228</v>
+      </c>
+      <c r="E127" t="s">
+        <v>101</v>
+      </c>
+      <c r="F127" t="s">
+        <v>101</v>
+      </c>
+      <c r="H127" s="2" t="s">
         <v>806</v>
-      </c>
-      <c r="C127" t="s">
-        <v>807</v>
-      </c>
-      <c r="D127" t="s">
-        <v>228</v>
-      </c>
-      <c r="E127" t="s">
-        <v>808</v>
-      </c>
-      <c r="F127" t="s">
-        <v>258</v>
-      </c>
-      <c r="H127" s="2" t="s">
-        <v>809</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>807</v>
+      </c>
+      <c r="B128" t="s">
+        <v>808</v>
+      </c>
+      <c r="C128" t="s">
+        <v>215</v>
+      </c>
+      <c r="D128" t="s">
+        <v>228</v>
+      </c>
+      <c r="E128" t="s">
+        <v>809</v>
+      </c>
+      <c r="F128" t="s">
         <v>810</v>
-      </c>
-      <c r="B128" t="s">
-        <v>538</v>
-      </c>
-      <c r="C128" t="s">
-        <v>539</v>
-      </c>
-      <c r="D128" t="s">
-        <v>228</v>
-      </c>
-      <c r="E128" t="s">
-        <v>681</v>
-      </c>
-      <c r="F128" t="s">
-        <v>541</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>811</v>
@@ -7073,16 +7097,16 @@
         <v>813</v>
       </c>
       <c r="C129" t="s">
-        <v>315</v>
+        <v>814</v>
       </c>
       <c r="D129" t="s">
         <v>228</v>
       </c>
       <c r="E129" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="F129" t="s">
-        <v>815</v>
+        <v>258</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>816</v>
@@ -7093,275 +7117,275 @@
         <v>817</v>
       </c>
       <c r="B130" t="s">
+        <v>543</v>
+      </c>
+      <c r="C130" t="s">
+        <v>544</v>
+      </c>
+      <c r="D130" t="s">
+        <v>228</v>
+      </c>
+      <c r="E130" t="s">
+        <v>688</v>
+      </c>
+      <c r="F130" t="s">
+        <v>546</v>
+      </c>
+      <c r="H130" s="2" t="s">
         <v>818</v>
-      </c>
-      <c r="C130" t="s">
-        <v>819</v>
-      </c>
-      <c r="D130" t="s">
-        <v>250</v>
-      </c>
-      <c r="E130" t="s">
-        <v>820</v>
-      </c>
-      <c r="F130" t="s">
-        <v>821</v>
-      </c>
-      <c r="H130" s="2" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="B131" t="s">
-        <v>824</v>
+        <v>548</v>
       </c>
       <c r="C131" t="s">
-        <v>825</v>
+        <v>544</v>
       </c>
       <c r="D131" t="s">
         <v>228</v>
       </c>
       <c r="E131" t="s">
-        <v>826</v>
+        <v>688</v>
       </c>
       <c r="F131" t="s">
-        <v>827</v>
+        <v>546</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>828</v>
+        <v>819</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
+        <v>820</v>
+      </c>
+      <c r="B132" t="s">
+        <v>821</v>
+      </c>
+      <c r="C132" t="s">
+        <v>315</v>
+      </c>
+      <c r="D132" t="s">
+        <v>228</v>
+      </c>
+      <c r="E132" t="s">
+        <v>822</v>
+      </c>
+      <c r="F132" t="s">
         <v>823</v>
       </c>
-      <c r="B132" t="s">
+      <c r="H132" s="2" t="s">
         <v>824</v>
-      </c>
-      <c r="C132" t="s">
-        <v>829</v>
-      </c>
-      <c r="D132" t="s">
-        <v>228</v>
-      </c>
-      <c r="E132" t="s">
-        <v>826</v>
-      </c>
-      <c r="F132" t="s">
-        <v>827</v>
-      </c>
-      <c r="H132" s="2" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>831</v>
+        <v>825</v>
       </c>
       <c r="B133" t="s">
-        <v>426</v>
+        <v>826</v>
       </c>
       <c r="C133" t="s">
-        <v>78</v>
+        <v>827</v>
       </c>
       <c r="D133" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="E133" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="F133" t="s">
-        <v>428</v>
+        <v>829</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
+        <v>831</v>
+      </c>
+      <c r="B134" t="s">
+        <v>832</v>
+      </c>
+      <c r="C134" t="s">
+        <v>833</v>
+      </c>
+      <c r="D134" t="s">
+        <v>228</v>
+      </c>
+      <c r="E134" t="s">
         <v>834</v>
       </c>
-      <c r="B134" t="s">
+      <c r="F134" t="s">
         <v>835</v>
       </c>
-      <c r="C134" t="s">
+      <c r="H134" s="2" t="s">
         <v>836</v>
-      </c>
-      <c r="D134" t="s">
-        <v>228</v>
-      </c>
-      <c r="E134" t="s">
-        <v>837</v>
-      </c>
-      <c r="F134" t="s">
-        <v>838</v>
-      </c>
-      <c r="H134" s="2" t="s">
-        <v>839</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>840</v>
+        <v>831</v>
       </c>
       <c r="B135" t="s">
-        <v>841</v>
+        <v>832</v>
       </c>
       <c r="C135" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="D135" t="s">
         <v>228</v>
       </c>
       <c r="E135" t="s">
-        <v>843</v>
+        <v>834</v>
       </c>
       <c r="F135" t="s">
-        <v>844</v>
+        <v>835</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>845</v>
+        <v>838</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>846</v>
+        <v>839</v>
       </c>
       <c r="B136" t="s">
-        <v>847</v>
+        <v>432</v>
       </c>
       <c r="C136" t="s">
-        <v>848</v>
+        <v>78</v>
       </c>
       <c r="D136" t="s">
-        <v>482</v>
+        <v>228</v>
       </c>
       <c r="E136" t="s">
-        <v>849</v>
+        <v>840</v>
       </c>
       <c r="F136" t="s">
-        <v>101</v>
+        <v>434</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>850</v>
+        <v>841</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>851</v>
+        <v>842</v>
       </c>
       <c r="B137" t="s">
+        <v>843</v>
+      </c>
+      <c r="C137" t="s">
+        <v>844</v>
+      </c>
+      <c r="D137" t="s">
+        <v>228</v>
+      </c>
+      <c r="E137" t="s">
+        <v>845</v>
+      </c>
+      <c r="F137" t="s">
+        <v>846</v>
+      </c>
+      <c r="H137" s="2" t="s">
         <v>847</v>
-      </c>
-      <c r="C137" t="s">
-        <v>848</v>
-      </c>
-      <c r="D137" t="s">
-        <v>482</v>
-      </c>
-      <c r="E137" t="s">
-        <v>852</v>
-      </c>
-      <c r="F137" t="s">
-        <v>101</v>
-      </c>
-      <c r="H137" s="2" t="s">
-        <v>853</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="B138" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="C138" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="D138" t="s">
-        <v>482</v>
+        <v>228</v>
       </c>
       <c r="E138" t="s">
-        <v>857</v>
+        <v>851</v>
       </c>
       <c r="F138" t="s">
-        <v>101</v>
+        <v>852</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="B139" t="s">
-        <v>623</v>
+        <v>855</v>
       </c>
       <c r="C139" t="s">
-        <v>215</v>
+        <v>856</v>
       </c>
       <c r="D139" t="s">
-        <v>228</v>
+        <v>488</v>
       </c>
       <c r="E139" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="F139" t="s">
-        <v>625</v>
+        <v>101</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="B140" t="s">
-        <v>863</v>
+        <v>855</v>
       </c>
       <c r="C140" t="s">
-        <v>375</v>
+        <v>856</v>
       </c>
       <c r="D140" t="s">
-        <v>228</v>
+        <v>488</v>
       </c>
       <c r="E140" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="F140" t="s">
-        <v>865</v>
+        <v>101</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="B141" t="s">
         <v>863</v>
       </c>
       <c r="C141" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="D141" t="s">
-        <v>228</v>
+        <v>488</v>
       </c>
       <c r="E141" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="F141" t="s">
-        <v>865</v>
+        <v>101</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -7369,22 +7393,91 @@
         <v>867</v>
       </c>
       <c r="B142" t="s">
-        <v>863</v>
+        <v>630</v>
       </c>
       <c r="C142" t="s">
-        <v>375</v>
+        <v>215</v>
       </c>
       <c r="D142" t="s">
         <v>228</v>
       </c>
       <c r="E142" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="F142" t="s">
-        <v>865</v>
+        <v>632</v>
       </c>
       <c r="H142" s="2" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>870</v>
+      </c>
+      <c r="B143" t="s">
         <v>871</v>
+      </c>
+      <c r="C143" t="s">
+        <v>381</v>
+      </c>
+      <c r="D143" t="s">
+        <v>228</v>
+      </c>
+      <c r="E143" t="s">
+        <v>872</v>
+      </c>
+      <c r="F143" t="s">
+        <v>873</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>875</v>
+      </c>
+      <c r="B144" t="s">
+        <v>871</v>
+      </c>
+      <c r="C144" t="s">
+        <v>876</v>
+      </c>
+      <c r="D144" t="s">
+        <v>228</v>
+      </c>
+      <c r="E144" t="s">
+        <v>877</v>
+      </c>
+      <c r="F144" t="s">
+        <v>873</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>875</v>
+      </c>
+      <c r="B145" t="s">
+        <v>871</v>
+      </c>
+      <c r="C145" t="s">
+        <v>381</v>
+      </c>
+      <c r="D145" t="s">
+        <v>228</v>
+      </c>
+      <c r="E145" t="s">
+        <v>872</v>
+      </c>
+      <c r="F145" t="s">
+        <v>873</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>879</v>
       </c>
     </row>
   </sheetData>
@@ -7531,6 +7624,9 @@
     <hyperlink ref="H140" r:id="rId139"/>
     <hyperlink ref="H141" r:id="rId140"/>
     <hyperlink ref="H142" r:id="rId141"/>
+    <hyperlink ref="H143" r:id="rId142"/>
+    <hyperlink ref="H144" r:id="rId143"/>
+    <hyperlink ref="H145" r:id="rId144"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
